--- a/Database.xlsx
+++ b/Database.xlsx
@@ -1,26 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11110"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aa/Documents/НОУКА/мигро в Чике/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2A68E82-9649-204A-9135-F15A521D2FF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="500" windowWidth="16100" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="773" uniqueCount="399">
   <si>
     <t>N</t>
   </si>
@@ -58,6 +52,9 @@
     <t>Longitude</t>
   </si>
   <si>
+    <t>Unnamed: 12</t>
+  </si>
+  <si>
     <t>1722 W Chicago ave</t>
   </si>
   <si>
@@ -82,6 +79,9 @@
     <t>5803 W Grand Ave</t>
   </si>
   <si>
+    <t>1890 S loomis st</t>
+  </si>
+  <si>
     <t>4204 Archer Ave</t>
   </si>
   <si>
@@ -106,6 +106,9 @@
     <t>1025 W 18th st</t>
   </si>
   <si>
+    <t>2657 W 15th Pl, Chicago, IL 60608</t>
+  </si>
+  <si>
     <t>1752 W Chicago Ave</t>
   </si>
   <si>
@@ -151,12 +154,18 @@
     <t>1346 S Halsted St</t>
   </si>
   <si>
+    <t>1579 Milwaukee Ave</t>
+  </si>
+  <si>
     <t>2358 W Chicago Ave</t>
   </si>
   <si>
     <t xml:space="preserve">631 S Ashland Blvd </t>
   </si>
   <si>
+    <t>1402 N Paulina St</t>
+  </si>
+  <si>
     <t>2228 W Augusta</t>
   </si>
   <si>
@@ -181,6 +190,186 @@
     <t>2626 N 73rd st</t>
   </si>
   <si>
+    <t>1809 S Loomis St</t>
+  </si>
+  <si>
+    <t>2324 N 73rd Ave</t>
+  </si>
+  <si>
+    <t>33 N Halsted St</t>
+  </si>
+  <si>
+    <t>4841 Argyle St</t>
+  </si>
+  <si>
+    <t>1110 N Oakley Blvd</t>
+  </si>
+  <si>
+    <t>Corner of Madison and Clark St</t>
+  </si>
+  <si>
+    <t>1500 W Division St</t>
+  </si>
+  <si>
+    <t>1109 Madison St, Gary</t>
+  </si>
+  <si>
+    <t>1657 W 45th St</t>
+  </si>
+  <si>
+    <t>542 S Dearborn St</t>
+  </si>
+  <si>
+    <t>4701 W Roosevelt Rd</t>
+  </si>
+  <si>
+    <t>7534 W Madison St</t>
+  </si>
+  <si>
+    <t>2410 W Walton St</t>
+  </si>
+  <si>
+    <t>190 N State St</t>
+  </si>
+  <si>
+    <t>40 Wells st</t>
+  </si>
+  <si>
+    <t>2458 W Altgeld St</t>
+  </si>
+  <si>
+    <t>1467 W Erie St</t>
+  </si>
+  <si>
+    <t>31 S Clark St</t>
+  </si>
+  <si>
+    <t>3351 W 38 Pl</t>
+  </si>
+  <si>
+    <t>1626 S Washtenaw Ave</t>
+  </si>
+  <si>
+    <t>3314 W Roosevelt Rd</t>
+  </si>
+  <si>
+    <t>1943 W 51st st</t>
+  </si>
+  <si>
+    <t>1259 W 12th st</t>
+  </si>
+  <si>
+    <t>3508 Roosevelt Rd</t>
+  </si>
+  <si>
+    <t>1964 Milwaukee Ave</t>
+  </si>
+  <si>
+    <t>1240 N Roby St</t>
+  </si>
+  <si>
+    <t>2020 N Leavitt St</t>
+  </si>
+  <si>
+    <t>1408 S Union Ave</t>
+  </si>
+  <si>
+    <t>2326 W Chicago Ave</t>
+  </si>
+  <si>
+    <t>1937 S Kedzie Ave</t>
+  </si>
+  <si>
+    <t>2705 W North Ave</t>
+  </si>
+  <si>
+    <t>1082 Hermitage Ave</t>
+  </si>
+  <si>
+    <t>2647 W 18th st</t>
+  </si>
+  <si>
+    <t>1341 S Morgan</t>
+  </si>
+  <si>
+    <t>2609 W Ogden Ave</t>
+  </si>
+  <si>
+    <t>35 S Dearborn</t>
+  </si>
+  <si>
+    <t>2223 W Chicago Ave</t>
+  </si>
+  <si>
+    <t>2106 W Chicago Ave</t>
+  </si>
+  <si>
+    <t>2201 W Chicago Ave</t>
+  </si>
+  <si>
+    <t>138 Passaic St</t>
+  </si>
+  <si>
+    <t>3131 West 42th st</t>
+  </si>
+  <si>
+    <t>1027 Milwaukee ave</t>
+  </si>
+  <si>
+    <t>1808 S Ashland Ave</t>
+  </si>
+  <si>
+    <t>1923 W Division St</t>
+  </si>
+  <si>
+    <t>127 N Dearborn St</t>
+  </si>
+  <si>
+    <t>809 W 35th St</t>
+  </si>
+  <si>
+    <t>813 N Paulina St</t>
+  </si>
+  <si>
+    <t>3451 N Avers Ave</t>
+  </si>
+  <si>
+    <t>5539 W Belmont</t>
+  </si>
+  <si>
+    <t>3152 W Roosevelt Rd</t>
+  </si>
+  <si>
+    <t>1017 N Wood</t>
+  </si>
+  <si>
+    <t>2057 W 22 st</t>
+  </si>
+  <si>
+    <t>624 S Michigan Ave</t>
+  </si>
+  <si>
+    <t>403 S Wabash Ave</t>
+  </si>
+  <si>
+    <t>1346 W 14th st</t>
+  </si>
+  <si>
+    <t>742 E 105 Pl</t>
+  </si>
+  <si>
+    <t>1200 N Ashland Ave</t>
+  </si>
+  <si>
+    <t>1553 W Chicago Ave</t>
+  </si>
+  <si>
+    <t>614 State St</t>
+  </si>
+  <si>
+    <t>310 S Michigan Ave</t>
+  </si>
+  <si>
     <t>книги</t>
   </si>
   <si>
@@ -235,6 +424,27 @@
     <t>студия</t>
   </si>
   <si>
+    <t>продажа вещей</t>
+  </si>
+  <si>
+    <t>финансы</t>
+  </si>
+  <si>
+    <t>потребительские товары</t>
+  </si>
+  <si>
+    <t>ремесленник</t>
+  </si>
+  <si>
+    <t>аптека</t>
+  </si>
+  <si>
+    <t>нотариус</t>
+  </si>
+  <si>
+    <t>ресторан</t>
+  </si>
+  <si>
     <t>Russian Daily Herald Rassvet // Русский Вестник</t>
   </si>
   <si>
@@ -355,6 +565,159 @@
     <t>Taran</t>
   </si>
   <si>
+    <t>Виттерт</t>
+  </si>
+  <si>
+    <t>Басиста</t>
+  </si>
+  <si>
+    <t>Novak</t>
+  </si>
+  <si>
+    <t>частное объявление</t>
+  </si>
+  <si>
+    <t>Zaren</t>
+  </si>
+  <si>
+    <t>H.O. Stone Co.</t>
+  </si>
+  <si>
+    <t>Division Employment Agency</t>
+  </si>
+  <si>
+    <t>Grabinski</t>
+  </si>
+  <si>
+    <t>Русско-турецкая баня</t>
+  </si>
+  <si>
+    <t>Czesna</t>
+  </si>
+  <si>
+    <t>Wasleff</t>
+  </si>
+  <si>
+    <t>Nemtzow</t>
+  </si>
+  <si>
+    <t>Amelianovich</t>
+  </si>
+  <si>
+    <t>Шуран</t>
+  </si>
+  <si>
+    <t>Walder</t>
+  </si>
+  <si>
+    <t>Gill</t>
+  </si>
+  <si>
+    <t>Прокопик</t>
+  </si>
+  <si>
+    <t>Войцицкая</t>
+  </si>
+  <si>
+    <t>Ишкин и Маринин</t>
+  </si>
+  <si>
+    <t>Каминский</t>
+  </si>
+  <si>
+    <t>Циглер и сын</t>
+  </si>
+  <si>
+    <t>Эпстейн</t>
+  </si>
+  <si>
+    <t>Изакович</t>
+  </si>
+  <si>
+    <t>Копнагель</t>
+  </si>
+  <si>
+    <t>Польская интеллигентная семья</t>
+  </si>
+  <si>
+    <t>Панасюк</t>
+  </si>
+  <si>
+    <t>Jaworek</t>
+  </si>
+  <si>
+    <t>Dr Bank</t>
+  </si>
+  <si>
+    <t>Kanaski</t>
+  </si>
+  <si>
+    <t>Dr Ross</t>
+  </si>
+  <si>
+    <t>Штейнберг</t>
+  </si>
+  <si>
+    <t>Schwetz Drug Store</t>
+  </si>
+  <si>
+    <t>A. Stetz Feather Co.</t>
+  </si>
+  <si>
+    <t>Пивень</t>
+  </si>
+  <si>
+    <t>Bednarz</t>
+  </si>
+  <si>
+    <t>Strnad</t>
+  </si>
+  <si>
+    <t>Zavertnik</t>
+  </si>
+  <si>
+    <t>S. L. Fabian and Co</t>
+  </si>
+  <si>
+    <t>Валтон</t>
+  </si>
+  <si>
+    <t>Frank Ryniecki and Co.</t>
+  </si>
+  <si>
+    <t>INDependence Construction Co</t>
+  </si>
+  <si>
+    <t>Др Гиман В Бау</t>
+  </si>
+  <si>
+    <t>Др Дж Зун</t>
+  </si>
+  <si>
+    <t>Др П. Л. Чадович</t>
+  </si>
+  <si>
+    <t>A S Plecho and Co</t>
+  </si>
+  <si>
+    <t>господин Лесик</t>
+  </si>
+  <si>
+    <t>ресторан Петрушка</t>
+  </si>
+  <si>
+    <t>Даниил Кот</t>
+  </si>
+  <si>
+    <t>Кселовский</t>
+  </si>
+  <si>
+    <t>П. Кворка и сыновья</t>
+  </si>
+  <si>
+    <t>Pierce Richard and Co</t>
+  </si>
+  <si>
     <t>Продажа книг</t>
   </si>
   <si>
@@ -424,18 +787,201 @@
     <t>старый русский врач</t>
   </si>
   <si>
+    <t>первое - адрес владельца, второе - адрес объекта(// 47 Place)</t>
+  </si>
+  <si>
     <t>ищу брата</t>
   </si>
   <si>
+    <t>Ассистент хирурга</t>
+  </si>
+  <si>
     <t>Акушерка/массажистка</t>
   </si>
   <si>
+    <t>требуется рабочий в русскую фирму</t>
+  </si>
+  <si>
     <t>контрактор-пейнтер</t>
   </si>
   <si>
     <t>оперная артистка/постановка голоса</t>
   </si>
   <si>
+    <t>Хиропрактор</t>
+  </si>
+  <si>
+    <t>адрес квартиры</t>
+  </si>
+  <si>
+    <t>Продается поддержанная русская пишущая машинка</t>
+  </si>
+  <si>
+    <t>продаются богалоус в 5 и 6 комнат</t>
+  </si>
+  <si>
+    <t>продается мебель</t>
+  </si>
+  <si>
+    <t>доход на сбережения</t>
+  </si>
+  <si>
+    <t>window washers, janitors, pantry girls…</t>
+  </si>
+  <si>
+    <t>требуются польские, русские и украинские джентельмены</t>
+  </si>
+  <si>
+    <t>русско-турецкие серные бани</t>
+  </si>
+  <si>
+    <t>советы, чертежи, сметы по постройке домов</t>
+  </si>
+  <si>
+    <t>краски, стройматериалы</t>
+  </si>
+  <si>
+    <t>требуется молодая женщина, должна уметь писать по-польски</t>
+  </si>
+  <si>
+    <t>Ищу партнера для бизнеса</t>
+  </si>
+  <si>
+    <t>Доставляю уголь и перевожу домашние вещи в Чикаго</t>
+  </si>
+  <si>
+    <t>Болезни желудка</t>
+  </si>
+  <si>
+    <t>ревматизм, простуда, экземы, сыпи</t>
+  </si>
+  <si>
+    <t>сдаются в наем две комнаты и гараж</t>
+  </si>
+  <si>
+    <t>требуется говорящая по-русски женщина</t>
+  </si>
+  <si>
+    <t>продается автомобиль</t>
+  </si>
+  <si>
+    <t>Контракторы и декораторы</t>
+  </si>
+  <si>
+    <t>Русский сапожник</t>
+  </si>
+  <si>
+    <t>строитель больших зданий</t>
+  </si>
+  <si>
+    <t>зубной</t>
+  </si>
+  <si>
+    <t>ревматизм, венерические и хронические болезни</t>
+  </si>
+  <si>
+    <t>в бездетной семье сдается фронтовая чистая комната</t>
+  </si>
+  <si>
+    <t>желаем взять двух интеллигентных человек на квартиру</t>
+  </si>
+  <si>
+    <t>продается бутчерня и гроссерня в польско-литовском районе</t>
+  </si>
+  <si>
+    <t>приглашаем всех русских женщин и барышен, которые хотят высматривать молоденькими и свежими</t>
+  </si>
+  <si>
+    <t>продается кирпичный дом, 9700 долларов</t>
+  </si>
+  <si>
+    <t>Изучение зубной техники</t>
+  </si>
+  <si>
+    <t>требуется первоклассный портной для первоклассной мужской одежды</t>
+  </si>
+  <si>
+    <t>Продается пекарня вместе с имуществом</t>
+  </si>
+  <si>
+    <t>продается биллиардная</t>
+  </si>
+  <si>
+    <t>продается обстановка для мясной лавки</t>
+  </si>
+  <si>
+    <t>общая практика</t>
+  </si>
+  <si>
+    <t>глазной специалист</t>
+  </si>
+  <si>
+    <t>комнаты в наем</t>
+  </si>
+  <si>
+    <t>продажа мебели</t>
+  </si>
+  <si>
+    <t>сдается комната в русской бездетной семье</t>
+  </si>
+  <si>
+    <t>готовые подушки и перины</t>
+  </si>
+  <si>
+    <t>5-ти комнатная мебель оптово или поштучно</t>
+  </si>
+  <si>
+    <t>продаются хроматические гармони, ручная работа, цены умеренные</t>
+  </si>
+  <si>
+    <t>Новый кирпичный бунгало за 2000 долларов</t>
+  </si>
+  <si>
+    <t>мясная лавка в бойком районе за 1/4 цены</t>
+  </si>
+  <si>
+    <t>Моргичес, нотариус, перевод денег</t>
+  </si>
+  <si>
+    <t>контракторы</t>
+  </si>
+  <si>
+    <t>Русская строительная контора</t>
+  </si>
+  <si>
+    <t>Ухо, нос и горло</t>
+  </si>
+  <si>
+    <t>продается бутчерня и гроссерня в польско-литовской колонии</t>
+  </si>
+  <si>
+    <t>Дешево продается мебель и новая белая печка</t>
+  </si>
+  <si>
+    <t>Продаем фармы, дома, торговые предприятия</t>
+  </si>
+  <si>
+    <t>требуются для легкой и выгодной работы мужчины и женщины со знанием русского языка</t>
+  </si>
+  <si>
+    <t>требуется швейцар</t>
+  </si>
+  <si>
+    <t>русский портной</t>
+  </si>
+  <si>
+    <t>русский плотник</t>
+  </si>
+  <si>
+    <t>Мебель, печи, пианино, костюмы за наличные и в рассрочку</t>
+  </si>
+  <si>
+    <t>продается весьма доходное имущество, 5 квартир, водяное отопление, 3 местный гараж</t>
+  </si>
+  <si>
+    <t>Требуется стенографистка</t>
+  </si>
+  <si>
     <t>Rassvet =: The dawn</t>
   </si>
   <si>
@@ -631,29 +1177,47 @@
     <t>https://www.loc.gov/resource/sn82015743/1927-04-01/ed-1/?sp=3</t>
   </si>
   <si>
-    <t>1890 S loomis st</t>
-  </si>
-  <si>
-    <t>2657 W 15th Pl, Chicago, IL 60608</t>
-  </si>
-  <si>
-    <t>1579 Milwaukee Ave</t>
-  </si>
-  <si>
-    <t>1402 N Paulina St</t>
-  </si>
-  <si>
-    <t>первое - адрес владельца, второе - адрес объекта(// 47 Place)</t>
-  </si>
-  <si>
-    <t>требуется рабочий в русскую фирму</t>
+    <t>https://www.loc.gov/resource/sn82015743/1927-04-01/ed-1/?sp=4</t>
+  </si>
+  <si>
+    <t>https://www.loc.gov/resource/sn82015743/1927-04-01/ed-1/?sp=5</t>
+  </si>
+  <si>
+    <t>https://www.loc.gov/resource/sn82015743/1927-04-01/ed-1/?sp=6</t>
+  </si>
+  <si>
+    <t>https://www.loc.gov/resource/sn82015743/1927-04-01/ed-1/?sp=7</t>
+  </si>
+  <si>
+    <t>https://www.loc.gov/resource/sn82015743/1927-04-01/ed-1/?sp=8</t>
+  </si>
+  <si>
+    <t>https://www.loc.gov/resource/sn82015743/1927-04-01/ed-1/?sp=9</t>
+  </si>
+  <si>
+    <t>https://www.loc.gov/resource/sn82015743/1927-04-01/ed-1/?sp=10</t>
+  </si>
+  <si>
+    <t>https://www.loc.gov/resource/sn82015743/1927-04-01/ed-1/?sp=11</t>
+  </si>
+  <si>
+    <t>https://www.loc.gov/resource/sn82015743/1927-04-01/ed-1/?sp=12</t>
+  </si>
+  <si>
+    <t>https://www.loc.gov/resource/sn82015743/1927-04-01/ed-1/?sp=13</t>
+  </si>
+  <si>
+    <t>https://www.loc.gov/resource/sn82015743/1927-04-01/ed-1/?sp=14</t>
+  </si>
+  <si>
+    <t>Unsure</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -724,26 +1288,18 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Гиперссылка" xfId="1" builtinId="8"/>
-    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -781,7 +1337,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -815,7 +1371,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -850,10 +1405,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1026,11 +1580,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L90"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M140"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:13">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1067,25 +1621,28 @@
       <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>53</v>
+        <v>118</v>
       </c>
       <c r="D2" t="s">
-        <v>71</v>
+        <v>143</v>
       </c>
       <c r="E2" t="s">
-        <v>111</v>
+        <v>234</v>
       </c>
       <c r="F2" t="s">
-        <v>138</v>
+        <v>322</v>
       </c>
       <c r="G2">
         <v>1926</v>
@@ -1097,30 +1654,30 @@
         <v>1</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>139</v>
+        <v>323</v>
       </c>
       <c r="K2">
-        <v>41.896288699999999</v>
+        <v>41.8962887</v>
       </c>
       <c r="L2">
-        <v>-87.670764800000001</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
+        <v>-87.6707648</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>54</v>
+        <v>119</v>
       </c>
       <c r="D3" t="s">
-        <v>72</v>
+        <v>144</v>
       </c>
       <c r="F3" t="s">
-        <v>138</v>
+        <v>322</v>
       </c>
       <c r="G3">
         <v>1926</v>
@@ -1132,27 +1689,27 @@
         <v>1</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>54</v>
+        <v>119</v>
       </c>
       <c r="D4" t="s">
-        <v>73</v>
+        <v>145</v>
       </c>
       <c r="E4" t="s">
-        <v>112</v>
+        <v>235</v>
       </c>
       <c r="F4" t="s">
-        <v>138</v>
+        <v>322</v>
       </c>
       <c r="G4">
         <v>1926</v>
@@ -1164,33 +1721,33 @@
         <v>1</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>141</v>
+        <v>325</v>
       </c>
       <c r="K4">
         <v>41.844355</v>
       </c>
       <c r="L4">
-        <v>-87.723045499999998</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+        <v>-87.7230455</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="D5" t="s">
-        <v>74</v>
+        <v>146</v>
       </c>
       <c r="E5" t="s">
-        <v>113</v>
+        <v>236</v>
       </c>
       <c r="F5" t="s">
-        <v>138</v>
+        <v>322</v>
       </c>
       <c r="G5">
         <v>1926</v>
@@ -1202,33 +1759,33 @@
         <v>1</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>142</v>
+        <v>326</v>
       </c>
       <c r="K5">
-        <v>41.541231699999997</v>
+        <v>41.5412317</v>
       </c>
       <c r="L5">
-        <v>-87.635366099999999</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+        <v>-87.6353661</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>56</v>
+        <v>121</v>
       </c>
       <c r="D6" t="s">
-        <v>75</v>
+        <v>147</v>
       </c>
       <c r="E6" t="s">
-        <v>114</v>
+        <v>237</v>
       </c>
       <c r="F6" t="s">
-        <v>138</v>
+        <v>322</v>
       </c>
       <c r="G6">
         <v>1926</v>
@@ -1240,33 +1797,33 @@
         <v>1</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>143</v>
+        <v>327</v>
       </c>
       <c r="K6">
-        <v>41.851602399999997</v>
+        <v>41.8516024</v>
       </c>
       <c r="L6">
-        <v>-87.721205900000001</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+        <v>-87.7212059</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C7" t="s">
-        <v>54</v>
+        <v>119</v>
       </c>
       <c r="D7" t="s">
-        <v>76</v>
+        <v>148</v>
       </c>
       <c r="E7" t="s">
-        <v>115</v>
+        <v>238</v>
       </c>
       <c r="F7" t="s">
-        <v>138</v>
+        <v>322</v>
       </c>
       <c r="G7">
         <v>1926</v>
@@ -1278,33 +1835,33 @@
         <v>1</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>144</v>
+        <v>328</v>
       </c>
       <c r="K7">
-        <v>41.902518499999999</v>
+        <v>41.9025185</v>
       </c>
       <c r="L7">
-        <v>-87.665625399999996</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+        <v>-87.6656254</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C8" t="s">
-        <v>54</v>
+        <v>119</v>
       </c>
       <c r="D8" t="s">
-        <v>77</v>
+        <v>149</v>
       </c>
       <c r="E8" t="s">
-        <v>116</v>
+        <v>239</v>
       </c>
       <c r="F8" t="s">
-        <v>138</v>
+        <v>322</v>
       </c>
       <c r="G8">
         <v>1926</v>
@@ -1316,33 +1873,33 @@
         <v>1</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>145</v>
+        <v>329</v>
       </c>
       <c r="K8">
-        <v>41.504779300000003</v>
+        <v>41.5047793</v>
       </c>
       <c r="L8">
-        <v>-87.560237700000002</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+        <v>-87.5602377</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C9" t="s">
-        <v>54</v>
+        <v>119</v>
       </c>
       <c r="D9" t="s">
-        <v>77</v>
+        <v>149</v>
       </c>
       <c r="E9" t="s">
-        <v>116</v>
+        <v>239</v>
       </c>
       <c r="F9" t="s">
-        <v>138</v>
+        <v>322</v>
       </c>
       <c r="G9">
         <v>1926</v>
@@ -1354,33 +1911,33 @@
         <v>1</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>145</v>
+        <v>329</v>
       </c>
       <c r="K9">
-        <v>41.919617199999998</v>
+        <v>41.9196172</v>
       </c>
       <c r="L9">
-        <v>-87.770944499999999</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+        <v>-87.7709445</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>203</v>
+        <v>21</v>
       </c>
       <c r="C10" t="s">
-        <v>54</v>
+        <v>119</v>
       </c>
       <c r="D10" t="s">
-        <v>78</v>
+        <v>150</v>
       </c>
       <c r="E10" t="s">
-        <v>117</v>
+        <v>240</v>
       </c>
       <c r="F10" t="s">
-        <v>138</v>
+        <v>322</v>
       </c>
       <c r="G10">
         <v>1926</v>
@@ -1392,27 +1949,33 @@
         <v>1</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+        <v>330</v>
+      </c>
+      <c r="K10">
+        <v>41.8562271</v>
+      </c>
+      <c r="L10">
+        <v>-87.6613828</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C11" t="s">
-        <v>54</v>
+        <v>119</v>
       </c>
       <c r="D11" t="s">
-        <v>79</v>
+        <v>151</v>
       </c>
       <c r="E11" t="s">
-        <v>118</v>
+        <v>241</v>
       </c>
       <c r="F11" t="s">
-        <v>138</v>
+        <v>322</v>
       </c>
       <c r="G11">
         <v>1926</v>
@@ -1424,33 +1987,33 @@
         <v>1</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>147</v>
+        <v>331</v>
       </c>
       <c r="K11">
-        <v>41.816989499999998</v>
+        <v>41.8169895</v>
       </c>
       <c r="L11">
         <v>-87.6996915</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:13">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C12" t="s">
-        <v>54</v>
+        <v>119</v>
       </c>
       <c r="D12" t="s">
-        <v>79</v>
+        <v>151</v>
       </c>
       <c r="E12" t="s">
-        <v>118</v>
+        <v>241</v>
       </c>
       <c r="F12" t="s">
-        <v>138</v>
+        <v>322</v>
       </c>
       <c r="G12">
         <v>1926</v>
@@ -1462,33 +2025,33 @@
         <v>1</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>147</v>
+        <v>331</v>
       </c>
       <c r="K12">
-        <v>41.903359399999999</v>
+        <v>41.9033594</v>
       </c>
       <c r="L12">
-        <v>-87.671688200000006</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+        <v>-87.67168820000001</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C13" t="s">
-        <v>54</v>
+        <v>119</v>
       </c>
       <c r="D13" t="s">
-        <v>80</v>
+        <v>152</v>
       </c>
       <c r="E13" t="s">
-        <v>119</v>
+        <v>242</v>
       </c>
       <c r="F13" t="s">
-        <v>138</v>
+        <v>322</v>
       </c>
       <c r="G13">
         <v>1926</v>
@@ -1500,33 +2063,33 @@
         <v>1</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>148</v>
+        <v>332</v>
       </c>
       <c r="K13">
-        <v>42.011494499999998</v>
+        <v>42.0114945</v>
       </c>
       <c r="L13">
-        <v>-87.670155399999999</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+        <v>-87.6701554</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C14" t="s">
-        <v>54</v>
+        <v>119</v>
       </c>
       <c r="D14" t="s">
-        <v>80</v>
+        <v>152</v>
       </c>
       <c r="E14" t="s">
-        <v>119</v>
+        <v>242</v>
       </c>
       <c r="F14" t="s">
-        <v>138</v>
+        <v>322</v>
       </c>
       <c r="G14">
         <v>1926</v>
@@ -1538,33 +2101,33 @@
         <v>1</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>148</v>
+        <v>332</v>
       </c>
       <c r="K14">
-        <v>41.881838600000002</v>
+        <v>41.8818386</v>
       </c>
       <c r="L14">
-        <v>-87.625746199999995</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+        <v>-87.62574619999999</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C15" t="s">
-        <v>54</v>
+        <v>119</v>
       </c>
       <c r="D15" t="s">
-        <v>81</v>
+        <v>153</v>
       </c>
       <c r="E15" t="s">
-        <v>85</v>
+        <v>157</v>
       </c>
       <c r="F15" t="s">
-        <v>138</v>
+        <v>322</v>
       </c>
       <c r="G15">
         <v>1926</v>
@@ -1576,33 +2139,33 @@
         <v>1</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>149</v>
+        <v>333</v>
       </c>
       <c r="K15">
-        <v>41.858081200000001</v>
+        <v>41.8580812</v>
       </c>
       <c r="L15">
         <v>-87.6605828</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:13">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C16" t="s">
-        <v>54</v>
+        <v>119</v>
       </c>
       <c r="D16" t="s">
-        <v>82</v>
+        <v>154</v>
       </c>
       <c r="E16" t="s">
-        <v>120</v>
+        <v>243</v>
       </c>
       <c r="F16" t="s">
-        <v>138</v>
+        <v>322</v>
       </c>
       <c r="G16">
         <v>1926</v>
@@ -1614,30 +2177,30 @@
         <v>1</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>150</v>
+        <v>334</v>
       </c>
       <c r="K16">
-        <v>41.895791799999998</v>
+        <v>41.8957918</v>
       </c>
       <c r="L16">
-        <v>-87.670613900000006</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
+        <v>-87.67061390000001</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C17" t="s">
-        <v>54</v>
+        <v>119</v>
       </c>
       <c r="D17" t="s">
-        <v>83</v>
+        <v>155</v>
       </c>
       <c r="F17" t="s">
-        <v>138</v>
+        <v>322</v>
       </c>
       <c r="G17">
         <v>1926</v>
@@ -1649,33 +2212,33 @@
         <v>1</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>151</v>
+        <v>335</v>
       </c>
       <c r="K17">
         <v>41.9031728</v>
       </c>
       <c r="L17">
-        <v>-87.667264799999998</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
+        <v>-87.6672648</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C18" t="s">
-        <v>54</v>
+        <v>119</v>
       </c>
       <c r="D18" t="s">
-        <v>84</v>
+        <v>156</v>
       </c>
       <c r="E18" t="s">
-        <v>121</v>
+        <v>244</v>
       </c>
       <c r="F18" t="s">
-        <v>138</v>
+        <v>322</v>
       </c>
       <c r="G18">
         <v>1926</v>
@@ -1687,33 +2250,33 @@
         <v>1</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>152</v>
+        <v>336</v>
       </c>
       <c r="K18">
-        <v>41.857925899999998</v>
+        <v>41.8579259</v>
       </c>
       <c r="L18">
-        <v>-87.652373900000001</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
+        <v>-87.6523739</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>204</v>
+        <v>30</v>
       </c>
       <c r="C19" t="s">
-        <v>57</v>
+        <v>122</v>
       </c>
       <c r="D19" t="s">
-        <v>85</v>
+        <v>157</v>
       </c>
       <c r="E19" t="s">
-        <v>122</v>
+        <v>245</v>
       </c>
       <c r="F19" t="s">
-        <v>138</v>
+        <v>322</v>
       </c>
       <c r="G19">
         <v>1926</v>
@@ -1725,33 +2288,33 @@
         <v>1</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>153</v>
+        <v>337</v>
       </c>
       <c r="K19">
         <v>41.8598807692427</v>
       </c>
       <c r="L19">
-        <v>-87.692528625263293</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
+        <v>-87.69252862526329</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C20" t="s">
-        <v>58</v>
+        <v>123</v>
       </c>
       <c r="D20" t="s">
-        <v>85</v>
+        <v>157</v>
       </c>
       <c r="E20" t="s">
-        <v>123</v>
+        <v>246</v>
       </c>
       <c r="F20" t="s">
-        <v>138</v>
+        <v>322</v>
       </c>
       <c r="G20">
         <v>1926</v>
@@ -1763,33 +2326,33 @@
         <v>1</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>154</v>
+        <v>338</v>
       </c>
       <c r="K20">
-        <v>41.896086199999999</v>
+        <v>41.8960862</v>
       </c>
       <c r="L20">
-        <v>-87.671374599999993</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
+        <v>-87.67137459999999</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C21" t="s">
-        <v>58</v>
+        <v>123</v>
       </c>
       <c r="D21" t="s">
-        <v>86</v>
+        <v>158</v>
       </c>
       <c r="E21" t="s">
-        <v>124</v>
+        <v>247</v>
       </c>
       <c r="F21" t="s">
-        <v>138</v>
+        <v>322</v>
       </c>
       <c r="G21">
         <v>1926</v>
@@ -1801,33 +2364,33 @@
         <v>1</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>155</v>
+        <v>339</v>
       </c>
       <c r="K21">
-        <v>41.909391800000002</v>
+        <v>41.9093918</v>
       </c>
       <c r="L21">
-        <v>-87.696927200000005</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
+        <v>-87.6969272</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12">
       <c r="A22">
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C22" t="s">
-        <v>59</v>
+        <v>124</v>
       </c>
       <c r="D22" t="s">
-        <v>87</v>
+        <v>159</v>
       </c>
       <c r="E22" t="s">
-        <v>125</v>
+        <v>248</v>
       </c>
       <c r="F22" t="s">
-        <v>138</v>
+        <v>322</v>
       </c>
       <c r="G22">
         <v>1926</v>
@@ -1839,33 +2402,33 @@
         <v>1</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>156</v>
+        <v>340</v>
       </c>
       <c r="K22">
-        <v>41.904816599999997</v>
+        <v>41.9048166</v>
       </c>
       <c r="L22">
-        <v>-87.683680899999999</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
+        <v>-87.6836809</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12">
       <c r="A23">
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C23" t="s">
-        <v>60</v>
+        <v>125</v>
       </c>
       <c r="D23" t="s">
-        <v>88</v>
+        <v>160</v>
       </c>
       <c r="E23" t="s">
-        <v>126</v>
+        <v>249</v>
       </c>
       <c r="F23" t="s">
-        <v>138</v>
+        <v>322</v>
       </c>
       <c r="G23">
         <v>1926</v>
@@ -1877,33 +2440,33 @@
         <v>1</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>157</v>
+        <v>341</v>
       </c>
       <c r="K23">
-        <v>41.881746300000003</v>
+        <v>41.8817463</v>
       </c>
       <c r="L23">
-        <v>-87.643403599999999</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
+        <v>-87.6434036</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12">
       <c r="A24">
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C24" t="s">
-        <v>60</v>
+        <v>125</v>
       </c>
       <c r="D24" t="s">
-        <v>89</v>
+        <v>161</v>
       </c>
       <c r="E24" t="s">
-        <v>127</v>
+        <v>250</v>
       </c>
       <c r="F24" t="s">
-        <v>138</v>
+        <v>322</v>
       </c>
       <c r="G24">
         <v>1926</v>
@@ -1915,30 +2478,30 @@
         <v>1</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>158</v>
+        <v>342</v>
       </c>
       <c r="K24">
-        <v>41.876896199999997</v>
+        <v>41.8768962</v>
       </c>
       <c r="L24">
-        <v>-87.625798000000003</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
+        <v>-87.625798</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12">
       <c r="A25">
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C25" t="s">
-        <v>61</v>
+        <v>126</v>
       </c>
       <c r="D25" t="s">
-        <v>90</v>
+        <v>162</v>
       </c>
       <c r="F25" t="s">
-        <v>138</v>
+        <v>322</v>
       </c>
       <c r="G25">
         <v>1926</v>
@@ -1950,30 +2513,30 @@
         <v>1</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>159</v>
+        <v>343</v>
       </c>
       <c r="K25">
-        <v>41.833657700000003</v>
+        <v>41.8336577</v>
       </c>
       <c r="L25">
-        <v>-87.645886500000003</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
+        <v>-87.6458865</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12">
       <c r="A26">
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C26" t="s">
-        <v>61</v>
+        <v>126</v>
       </c>
       <c r="D26" t="s">
-        <v>91</v>
+        <v>163</v>
       </c>
       <c r="F26" t="s">
-        <v>138</v>
+        <v>322</v>
       </c>
       <c r="G26">
         <v>1926</v>
@@ -1985,33 +2548,33 @@
         <v>1</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>160</v>
+        <v>344</v>
       </c>
       <c r="K26">
-        <v>41.895937099999998</v>
+        <v>41.8959371</v>
       </c>
       <c r="L26">
-        <v>-87.684590600000007</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
+        <v>-87.68459060000001</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12">
       <c r="A27">
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C27" t="s">
-        <v>62</v>
+        <v>127</v>
       </c>
       <c r="D27" t="s">
-        <v>92</v>
+        <v>164</v>
       </c>
       <c r="E27" t="s">
-        <v>128</v>
+        <v>251</v>
       </c>
       <c r="F27" t="s">
-        <v>138</v>
+        <v>322</v>
       </c>
       <c r="G27">
         <v>1926</v>
@@ -2023,33 +2586,33 @@
         <v>1</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>161</v>
+        <v>345</v>
       </c>
       <c r="K27">
-        <v>27.721699000000001</v>
+        <v>27.721699</v>
       </c>
       <c r="L27">
         <v>-81.5461308</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:12">
       <c r="A28">
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C28" t="s">
-        <v>62</v>
+        <v>127</v>
       </c>
       <c r="D28" t="s">
-        <v>93</v>
+        <v>165</v>
       </c>
       <c r="E28" t="s">
-        <v>129</v>
+        <v>252</v>
       </c>
       <c r="F28" t="s">
-        <v>138</v>
+        <v>322</v>
       </c>
       <c r="G28">
         <v>1926</v>
@@ -2061,30 +2624,30 @@
         <v>1</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>162</v>
+        <v>346</v>
       </c>
       <c r="K28">
-        <v>41.859632099999999</v>
+        <v>41.8596321</v>
       </c>
       <c r="L28">
-        <v>-87.668739799999997</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
+        <v>-87.6687398</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12">
       <c r="A29">
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C29" t="s">
-        <v>63</v>
+        <v>128</v>
       </c>
       <c r="D29" t="s">
-        <v>94</v>
+        <v>166</v>
       </c>
       <c r="F29" t="s">
-        <v>138</v>
+        <v>322</v>
       </c>
       <c r="G29">
         <v>1926</v>
@@ -2096,30 +2659,30 @@
         <v>1</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>163</v>
+        <v>347</v>
       </c>
       <c r="K29">
-        <v>41.895533700000001</v>
+        <v>41.8955337</v>
       </c>
       <c r="L29">
-        <v>-87.681686499999998</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.2">
+        <v>-87.6816865</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12">
       <c r="A30">
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C30" t="s">
-        <v>64</v>
+        <v>129</v>
       </c>
       <c r="D30" t="s">
-        <v>95</v>
+        <v>167</v>
       </c>
       <c r="F30" t="s">
-        <v>138</v>
+        <v>322</v>
       </c>
       <c r="G30">
         <v>1926</v>
@@ -2131,33 +2694,33 @@
         <v>1</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>164</v>
+        <v>348</v>
       </c>
       <c r="K30">
         <v>41.897447</v>
       </c>
       <c r="L30">
-        <v>-87.667116199999995</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
+        <v>-87.6671162</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12">
       <c r="A31">
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C31" t="s">
-        <v>65</v>
+        <v>130</v>
       </c>
       <c r="D31" t="s">
-        <v>96</v>
+        <v>168</v>
       </c>
       <c r="E31" t="s">
-        <v>130</v>
+        <v>253</v>
       </c>
       <c r="F31" t="s">
-        <v>138</v>
+        <v>322</v>
       </c>
       <c r="G31">
         <v>1926</v>
@@ -2169,33 +2732,33 @@
         <v>1</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>165</v>
+        <v>349</v>
       </c>
       <c r="K31">
-        <v>41.898370499999999</v>
+        <v>41.8983705</v>
       </c>
       <c r="L31">
-        <v>-87.671878300000003</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
+        <v>-87.6718783</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12">
       <c r="A32">
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C32" t="s">
-        <v>66</v>
+        <v>131</v>
       </c>
       <c r="D32" t="s">
-        <v>97</v>
+        <v>169</v>
       </c>
       <c r="E32" t="s">
-        <v>131</v>
+        <v>254</v>
       </c>
       <c r="F32" t="s">
-        <v>138</v>
+        <v>322</v>
       </c>
       <c r="G32">
         <v>1926</v>
@@ -2207,33 +2770,33 @@
         <v>15</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>166</v>
+        <v>350</v>
       </c>
       <c r="K32">
-        <v>41.898285100000003</v>
+        <v>41.8982851</v>
       </c>
       <c r="L32">
-        <v>-87.780121899999997</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.2">
+        <v>-87.7801219</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12">
       <c r="A33">
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C33" t="s">
-        <v>57</v>
+        <v>122</v>
       </c>
       <c r="D33" t="s">
-        <v>98</v>
+        <v>170</v>
       </c>
       <c r="E33" t="s">
-        <v>132</v>
+        <v>255</v>
       </c>
       <c r="F33" t="s">
-        <v>138</v>
+        <v>322</v>
       </c>
       <c r="G33">
         <v>1927</v>
@@ -2245,33 +2808,33 @@
         <v>3</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>167</v>
+        <v>351</v>
       </c>
       <c r="K33">
-        <v>41.863538800000001</v>
+        <v>41.8635388</v>
       </c>
       <c r="L33">
-        <v>-87.652638699999997</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.2">
+        <v>-87.6526387</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12">
       <c r="A34">
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C34" t="s">
-        <v>66</v>
+        <v>131</v>
       </c>
       <c r="D34" t="s">
-        <v>97</v>
+        <v>169</v>
       </c>
       <c r="E34" t="s">
-        <v>131</v>
+        <v>254</v>
       </c>
       <c r="F34" t="s">
-        <v>138</v>
+        <v>322</v>
       </c>
       <c r="G34">
         <v>1927</v>
@@ -2283,33 +2846,33 @@
         <v>3</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>168</v>
+        <v>352</v>
       </c>
       <c r="K34">
-        <v>41.898285100000003</v>
+        <v>41.8982851</v>
       </c>
       <c r="L34">
-        <v>-87.780121899999997</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.2">
+        <v>-87.7801219</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12">
       <c r="A35">
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C35" t="s">
-        <v>60</v>
+        <v>125</v>
       </c>
       <c r="D35" t="s">
-        <v>88</v>
+        <v>160</v>
       </c>
       <c r="E35" t="s">
-        <v>126</v>
+        <v>249</v>
       </c>
       <c r="F35" t="s">
-        <v>138</v>
+        <v>322</v>
       </c>
       <c r="G35">
         <v>1927</v>
@@ -2321,33 +2884,33 @@
         <v>3</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>169</v>
+        <v>353</v>
       </c>
       <c r="K35">
-        <v>41.881746300000003</v>
+        <v>41.8817463</v>
       </c>
       <c r="L35">
-        <v>-87.643403599999999</v>
-      </c>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.2">
+        <v>-87.6434036</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12">
       <c r="A36">
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C36" t="s">
-        <v>60</v>
+        <v>125</v>
       </c>
       <c r="D36" t="s">
-        <v>89</v>
+        <v>161</v>
       </c>
       <c r="E36" t="s">
-        <v>127</v>
+        <v>250</v>
       </c>
       <c r="F36" t="s">
-        <v>138</v>
+        <v>322</v>
       </c>
       <c r="G36">
         <v>1927</v>
@@ -2359,30 +2922,30 @@
         <v>3</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>170</v>
+        <v>354</v>
       </c>
       <c r="K36">
-        <v>41.876896199999997</v>
+        <v>41.8768962</v>
       </c>
       <c r="L36">
-        <v>-87.625798000000003</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.2">
+        <v>-87.625798</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12">
       <c r="A37">
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C37" t="s">
-        <v>61</v>
+        <v>126</v>
       </c>
       <c r="D37" t="s">
-        <v>90</v>
+        <v>162</v>
       </c>
       <c r="F37" t="s">
-        <v>138</v>
+        <v>322</v>
       </c>
       <c r="G37">
         <v>1927</v>
@@ -2394,30 +2957,30 @@
         <v>3</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>171</v>
+        <v>355</v>
       </c>
       <c r="K37">
-        <v>41.833657700000003</v>
+        <v>41.8336577</v>
       </c>
       <c r="L37">
-        <v>-87.645886500000003</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.2">
+        <v>-87.6458865</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12">
       <c r="A38">
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C38" t="s">
-        <v>61</v>
+        <v>126</v>
       </c>
       <c r="D38" t="s">
-        <v>91</v>
+        <v>163</v>
       </c>
       <c r="F38" t="s">
-        <v>138</v>
+        <v>322</v>
       </c>
       <c r="G38">
         <v>1927</v>
@@ -2429,30 +2992,30 @@
         <v>3</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>172</v>
+        <v>356</v>
       </c>
       <c r="K38">
-        <v>41.895937099999998</v>
+        <v>41.8959371</v>
       </c>
       <c r="L38">
-        <v>-87.684590600000007</v>
-      </c>
-    </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.2">
+        <v>-87.68459060000001</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12">
       <c r="A39">
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C39" t="s">
-        <v>62</v>
+        <v>127</v>
       </c>
       <c r="D39" t="s">
-        <v>92</v>
+        <v>164</v>
       </c>
       <c r="F39" t="s">
-        <v>138</v>
+        <v>322</v>
       </c>
       <c r="G39">
         <v>1927</v>
@@ -2464,30 +3027,30 @@
         <v>3</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>173</v>
+        <v>357</v>
       </c>
       <c r="K39">
-        <v>27.721699000000001</v>
+        <v>27.721699</v>
       </c>
       <c r="L39">
         <v>-81.5461308</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:12">
       <c r="A40">
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C40" t="s">
-        <v>62</v>
+        <v>127</v>
       </c>
       <c r="D40" t="s">
-        <v>93</v>
+        <v>165</v>
       </c>
       <c r="F40" t="s">
-        <v>138</v>
+        <v>322</v>
       </c>
       <c r="G40">
         <v>1927</v>
@@ -2499,30 +3062,30 @@
         <v>3</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>174</v>
+        <v>358</v>
       </c>
       <c r="K40">
-        <v>41.859632099999999</v>
+        <v>41.8596321</v>
       </c>
       <c r="L40">
-        <v>-87.668739799999997</v>
-      </c>
-    </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.2">
+        <v>-87.6687398</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12">
       <c r="A41">
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C41" t="s">
-        <v>63</v>
+        <v>128</v>
       </c>
       <c r="D41" t="s">
-        <v>94</v>
+        <v>166</v>
       </c>
       <c r="F41" t="s">
-        <v>138</v>
+        <v>322</v>
       </c>
       <c r="G41">
         <v>1927</v>
@@ -2534,30 +3097,30 @@
         <v>3</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>175</v>
+        <v>359</v>
       </c>
       <c r="K41">
-        <v>41.895533700000001</v>
+        <v>41.8955337</v>
       </c>
       <c r="L41">
-        <v>-87.681686499999998</v>
-      </c>
-    </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.2">
+        <v>-87.6816865</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12">
       <c r="A42">
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C42" t="s">
-        <v>64</v>
+        <v>129</v>
       </c>
       <c r="D42" t="s">
-        <v>95</v>
+        <v>167</v>
       </c>
       <c r="F42" t="s">
-        <v>138</v>
+        <v>322</v>
       </c>
       <c r="G42">
         <v>1927</v>
@@ -2569,30 +3132,30 @@
         <v>3</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>176</v>
+        <v>360</v>
       </c>
       <c r="K42">
         <v>41.897447</v>
       </c>
       <c r="L42">
-        <v>-87.667116199999995</v>
-      </c>
-    </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.2">
+        <v>-87.6671162</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12">
       <c r="A43">
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C43" t="s">
-        <v>65</v>
+        <v>130</v>
       </c>
       <c r="D43" t="s">
-        <v>96</v>
+        <v>168</v>
       </c>
       <c r="F43" t="s">
-        <v>138</v>
+        <v>322</v>
       </c>
       <c r="G43">
         <v>1927</v>
@@ -2604,33 +3167,33 @@
         <v>3</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>177</v>
+        <v>361</v>
       </c>
       <c r="K43">
-        <v>41.898370499999999</v>
+        <v>41.8983705</v>
       </c>
       <c r="L43">
-        <v>-87.671878300000003</v>
-      </c>
-    </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.2">
+        <v>-87.6718783</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12">
       <c r="A44">
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C44" t="s">
-        <v>54</v>
+        <v>119</v>
       </c>
       <c r="D44" t="s">
-        <v>99</v>
+        <v>171</v>
       </c>
       <c r="E44" t="s">
-        <v>119</v>
+        <v>242</v>
       </c>
       <c r="F44" t="s">
-        <v>138</v>
+        <v>322</v>
       </c>
       <c r="G44">
         <v>1927</v>
@@ -2642,33 +3205,33 @@
         <v>1</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>178</v>
+        <v>362</v>
       </c>
       <c r="K44">
-        <v>41.864015600000002</v>
+        <v>41.8640156</v>
       </c>
       <c r="L44">
-        <v>-87.646716699999999</v>
-      </c>
-    </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.2">
+        <v>-87.6467167</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12">
       <c r="A45">
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C45" t="s">
-        <v>54</v>
+        <v>119</v>
       </c>
       <c r="D45" t="s">
-        <v>99</v>
+        <v>171</v>
       </c>
       <c r="E45" t="s">
-        <v>119</v>
+        <v>242</v>
       </c>
       <c r="F45" t="s">
-        <v>138</v>
+        <v>322</v>
       </c>
       <c r="G45">
         <v>1927</v>
@@ -2680,33 +3243,33 @@
         <v>1</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>178</v>
+        <v>362</v>
       </c>
       <c r="K45">
-        <v>41.881838600000002</v>
+        <v>41.8818386</v>
       </c>
       <c r="L45">
-        <v>-87.625746199999995</v>
-      </c>
-    </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.2">
+        <v>-87.62574619999999</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12">
       <c r="A46">
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>205</v>
+        <v>46</v>
       </c>
       <c r="C46" t="s">
-        <v>54</v>
+        <v>119</v>
       </c>
       <c r="D46" t="s">
-        <v>100</v>
+        <v>172</v>
       </c>
       <c r="E46" t="s">
-        <v>133</v>
+        <v>256</v>
       </c>
       <c r="F46" t="s">
-        <v>138</v>
+        <v>322</v>
       </c>
       <c r="G46">
         <v>1927</v>
@@ -2718,27 +3281,33 @@
         <v>1</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.2">
+        <v>363</v>
+      </c>
+      <c r="K46">
+        <v>41.9101383</v>
+      </c>
+      <c r="L46">
+        <v>-87.6768273</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12">
       <c r="A47">
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C47" t="s">
-        <v>54</v>
+        <v>119</v>
       </c>
       <c r="D47" t="s">
-        <v>101</v>
+        <v>173</v>
       </c>
       <c r="E47" t="s">
-        <v>112</v>
+        <v>235</v>
       </c>
       <c r="F47" t="s">
-        <v>138</v>
+        <v>322</v>
       </c>
       <c r="G47">
         <v>1927</v>
@@ -2750,33 +3319,33 @@
         <v>1</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>180</v>
+        <v>364</v>
       </c>
       <c r="K47">
-        <v>41.895842199999997</v>
+        <v>41.8958422</v>
       </c>
       <c r="L47">
-        <v>-87.685816700000004</v>
-      </c>
-    </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.2">
+        <v>-87.6858167</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12">
       <c r="A48">
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C48" t="s">
-        <v>54</v>
+        <v>119</v>
       </c>
       <c r="D48" t="s">
-        <v>73</v>
+        <v>145</v>
       </c>
       <c r="E48" t="s">
-        <v>112</v>
+        <v>235</v>
       </c>
       <c r="F48" t="s">
-        <v>138</v>
+        <v>322</v>
       </c>
       <c r="G48">
         <v>1927</v>
@@ -2788,30 +3357,30 @@
         <v>1</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>181</v>
+        <v>365</v>
       </c>
       <c r="K48">
         <v>41.844355</v>
       </c>
       <c r="L48">
-        <v>-87.723045499999998</v>
-      </c>
-    </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.2">
+        <v>-87.7230455</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12">
       <c r="A49">
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C49" t="s">
-        <v>54</v>
+        <v>119</v>
       </c>
       <c r="D49" t="s">
-        <v>83</v>
+        <v>155</v>
       </c>
       <c r="F49" t="s">
-        <v>138</v>
+        <v>322</v>
       </c>
       <c r="G49">
         <v>1927</v>
@@ -2823,30 +3392,30 @@
         <v>1</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>182</v>
+        <v>366</v>
       </c>
       <c r="K49">
         <v>41.9031728</v>
       </c>
       <c r="L49">
-        <v>-87.667264799999998</v>
-      </c>
-    </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.2">
+        <v>-87.6672648</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12">
       <c r="A50">
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C50" t="s">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="D50" t="s">
-        <v>74</v>
+        <v>146</v>
       </c>
       <c r="F50" t="s">
-        <v>138</v>
+        <v>322</v>
       </c>
       <c r="G50">
         <v>1927</v>
@@ -2858,33 +3427,33 @@
         <v>1</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>183</v>
+        <v>367</v>
       </c>
       <c r="K50">
-        <v>41.541231699999997</v>
+        <v>41.5412317</v>
       </c>
       <c r="L50">
-        <v>-87.635366099999999</v>
-      </c>
-    </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.2">
+        <v>-87.6353661</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12">
       <c r="A51">
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C51" t="s">
-        <v>54</v>
+        <v>119</v>
       </c>
       <c r="D51" t="s">
-        <v>84</v>
+        <v>156</v>
       </c>
       <c r="E51" t="s">
-        <v>121</v>
+        <v>244</v>
       </c>
       <c r="F51" t="s">
-        <v>138</v>
+        <v>322</v>
       </c>
       <c r="G51">
         <v>1927</v>
@@ -2896,30 +3465,30 @@
         <v>1</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>184</v>
+        <v>368</v>
       </c>
       <c r="K51">
-        <v>41.857925899999998</v>
+        <v>41.8579259</v>
       </c>
       <c r="L51">
-        <v>-87.652373900000001</v>
-      </c>
-    </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.2">
+        <v>-87.6523739</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12">
       <c r="A52">
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>203</v>
+        <v>21</v>
       </c>
       <c r="C52" t="s">
-        <v>54</v>
+        <v>119</v>
       </c>
       <c r="D52" t="s">
-        <v>78</v>
+        <v>150</v>
       </c>
       <c r="F52" t="s">
-        <v>138</v>
+        <v>322</v>
       </c>
       <c r="G52">
         <v>1927</v>
@@ -2931,27 +3500,33 @@
         <v>1</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.2">
+        <v>369</v>
+      </c>
+      <c r="K52">
+        <v>41.8562271</v>
+      </c>
+      <c r="L52">
+        <v>-87.6613828</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12">
       <c r="A53">
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C53" t="s">
-        <v>54</v>
+        <v>119</v>
       </c>
       <c r="D53" t="s">
-        <v>79</v>
+        <v>151</v>
       </c>
       <c r="E53" t="s">
-        <v>118</v>
+        <v>241</v>
       </c>
       <c r="F53" t="s">
-        <v>138</v>
+        <v>322</v>
       </c>
       <c r="G53">
         <v>1927</v>
@@ -2963,33 +3538,33 @@
         <v>1</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>186</v>
+        <v>370</v>
       </c>
       <c r="K53">
-        <v>41.816989499999998</v>
+        <v>41.8169895</v>
       </c>
       <c r="L53">
         <v>-87.6996915</v>
       </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:12">
       <c r="A54">
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C54" t="s">
-        <v>54</v>
+        <v>119</v>
       </c>
       <c r="D54" t="s">
-        <v>79</v>
+        <v>151</v>
       </c>
       <c r="E54" t="s">
-        <v>118</v>
+        <v>241</v>
       </c>
       <c r="F54" t="s">
-        <v>138</v>
+        <v>322</v>
       </c>
       <c r="G54">
         <v>1927</v>
@@ -3001,33 +3576,33 @@
         <v>1</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>186</v>
+        <v>370</v>
       </c>
       <c r="K54">
-        <v>41.903359399999999</v>
+        <v>41.9033594</v>
       </c>
       <c r="L54">
-        <v>-87.671688200000006</v>
-      </c>
-    </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.2">
+        <v>-87.67168820000001</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12">
       <c r="A55">
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C55" t="s">
-        <v>54</v>
+        <v>119</v>
       </c>
       <c r="D55" t="s">
-        <v>80</v>
+        <v>152</v>
       </c>
       <c r="E55" t="s">
-        <v>119</v>
+        <v>242</v>
       </c>
       <c r="F55" t="s">
-        <v>138</v>
+        <v>322</v>
       </c>
       <c r="G55">
         <v>1927</v>
@@ -3039,33 +3614,33 @@
         <v>1</v>
       </c>
       <c r="J55" s="2" t="s">
-        <v>187</v>
+        <v>371</v>
       </c>
       <c r="K55">
-        <v>42.011494499999998</v>
+        <v>42.0114945</v>
       </c>
       <c r="L55">
-        <v>-87.670155399999999</v>
-      </c>
-    </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.2">
+        <v>-87.6701554</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12">
       <c r="A56">
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C56" t="s">
-        <v>54</v>
+        <v>119</v>
       </c>
       <c r="D56" t="s">
-        <v>80</v>
+        <v>152</v>
       </c>
       <c r="E56" t="s">
-        <v>119</v>
+        <v>242</v>
       </c>
       <c r="F56" t="s">
-        <v>138</v>
+        <v>322</v>
       </c>
       <c r="G56">
         <v>1927</v>
@@ -3077,33 +3652,33 @@
         <v>1</v>
       </c>
       <c r="J56" s="2" t="s">
-        <v>187</v>
+        <v>371</v>
       </c>
       <c r="K56">
-        <v>41.881838600000002</v>
+        <v>41.8818386</v>
       </c>
       <c r="L56">
-        <v>-87.625746199999995</v>
-      </c>
-    </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.2">
+        <v>-87.62574619999999</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12">
       <c r="A57">
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C57" t="s">
-        <v>54</v>
+        <v>119</v>
       </c>
       <c r="D57" t="s">
-        <v>81</v>
+        <v>153</v>
       </c>
       <c r="E57" t="s">
-        <v>85</v>
+        <v>157</v>
       </c>
       <c r="F57" t="s">
-        <v>138</v>
+        <v>322</v>
       </c>
       <c r="G57">
         <v>1927</v>
@@ -3115,33 +3690,33 @@
         <v>1</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>188</v>
+        <v>372</v>
       </c>
       <c r="K57">
-        <v>41.858081200000001</v>
+        <v>41.8580812</v>
       </c>
       <c r="L57">
         <v>-87.6605828</v>
       </c>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:12">
       <c r="A58">
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C58" t="s">
-        <v>54</v>
+        <v>119</v>
       </c>
       <c r="D58" t="s">
-        <v>82</v>
+        <v>154</v>
       </c>
       <c r="E58" t="s">
-        <v>120</v>
+        <v>243</v>
       </c>
       <c r="F58" t="s">
-        <v>138</v>
+        <v>322</v>
       </c>
       <c r="G58">
         <v>1927</v>
@@ -3153,33 +3728,33 @@
         <v>1</v>
       </c>
       <c r="J58" s="2" t="s">
-        <v>189</v>
+        <v>373</v>
       </c>
       <c r="K58">
-        <v>41.895791799999998</v>
+        <v>41.8957918</v>
       </c>
       <c r="L58">
-        <v>-87.670613900000006</v>
-      </c>
-    </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.2">
+        <v>-87.67061390000001</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12">
       <c r="A59">
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>206</v>
+        <v>49</v>
       </c>
       <c r="C59" t="s">
-        <v>67</v>
+        <v>132</v>
       </c>
       <c r="D59" t="s">
-        <v>85</v>
+        <v>157</v>
       </c>
       <c r="E59" t="s">
-        <v>207</v>
+        <v>257</v>
       </c>
       <c r="F59" t="s">
-        <v>138</v>
+        <v>322</v>
       </c>
       <c r="G59">
         <v>1927</v>
@@ -3191,24 +3766,30 @@
         <v>1</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.2">
+        <v>374</v>
+      </c>
+      <c r="K59">
+        <v>41.906892</v>
+      </c>
+      <c r="L59">
+        <v>-87.670137</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12">
       <c r="A60">
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="C60" t="s">
-        <v>58</v>
+        <v>123</v>
       </c>
       <c r="E60" t="s">
-        <v>123</v>
+        <v>246</v>
       </c>
       <c r="F60" t="s">
-        <v>138</v>
+        <v>322</v>
       </c>
       <c r="G60">
         <v>1927</v>
@@ -3220,33 +3801,33 @@
         <v>1</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>191</v>
+        <v>375</v>
       </c>
       <c r="K60">
-        <v>41.899687200000002</v>
+        <v>41.8996872</v>
       </c>
       <c r="L60">
-        <v>-87.683198300000001</v>
-      </c>
-    </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.2">
+        <v>-87.6831983</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12">
       <c r="A61">
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="C61" t="s">
-        <v>68</v>
+        <v>133</v>
       </c>
       <c r="D61" t="s">
-        <v>102</v>
+        <v>174</v>
       </c>
       <c r="E61" t="s">
-        <v>134</v>
+        <v>258</v>
       </c>
       <c r="F61" t="s">
-        <v>138</v>
+        <v>322</v>
       </c>
       <c r="G61">
         <v>1927</v>
@@ -3258,33 +3839,33 @@
         <v>1</v>
       </c>
       <c r="J61" s="2" t="s">
-        <v>192</v>
+        <v>376</v>
       </c>
       <c r="K61">
-        <v>41.863469299999998</v>
+        <v>41.8634693</v>
       </c>
       <c r="L61">
-        <v>-87.652251800000002</v>
-      </c>
-    </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.2">
+        <v>-87.6522518</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12">
       <c r="A62">
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C62" t="s">
-        <v>66</v>
+        <v>131</v>
       </c>
       <c r="D62" t="s">
-        <v>97</v>
+        <v>169</v>
       </c>
       <c r="E62" t="s">
-        <v>131</v>
+        <v>254</v>
       </c>
       <c r="F62" t="s">
-        <v>138</v>
+        <v>322</v>
       </c>
       <c r="G62">
         <v>1927</v>
@@ -3296,33 +3877,33 @@
         <v>1</v>
       </c>
       <c r="J62" s="2" t="s">
-        <v>193</v>
+        <v>377</v>
       </c>
       <c r="K62">
-        <v>41.898285100000003</v>
+        <v>41.8982851</v>
       </c>
       <c r="L62">
-        <v>-87.780121899999997</v>
-      </c>
-    </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.2">
+        <v>-87.7801219</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12">
       <c r="A63">
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C63" t="s">
-        <v>54</v>
+        <v>119</v>
       </c>
       <c r="D63" t="s">
-        <v>103</v>
+        <v>175</v>
       </c>
       <c r="E63" t="s">
-        <v>118</v>
+        <v>241</v>
       </c>
       <c r="F63" t="s">
-        <v>138</v>
+        <v>322</v>
       </c>
       <c r="G63">
         <v>1927</v>
@@ -3334,30 +3915,33 @@
         <v>1</v>
       </c>
       <c r="J63" s="2" t="s">
-        <v>194</v>
+        <v>378</v>
       </c>
       <c r="K63">
-        <v>41.864015600000002</v>
+        <v>41.8640156</v>
       </c>
       <c r="L63">
-        <v>-87.646716699999999</v>
-      </c>
-    </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.2">
+        <v>-87.6467167</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12">
       <c r="A64">
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="C64" t="s">
-        <v>54</v>
+        <v>119</v>
       </c>
       <c r="D64" t="s">
-        <v>104</v>
+        <v>176</v>
+      </c>
+      <c r="E64" t="s">
+        <v>259</v>
       </c>
       <c r="F64" t="s">
-        <v>138</v>
+        <v>322</v>
       </c>
       <c r="G64">
         <v>1927</v>
@@ -3369,33 +3953,33 @@
         <v>1</v>
       </c>
       <c r="J64" s="2" t="s">
-        <v>195</v>
+        <v>379</v>
       </c>
       <c r="K64">
-        <v>41.857485400000002</v>
+        <v>41.8574854</v>
       </c>
       <c r="L64">
-        <v>-87.694647000000003</v>
-      </c>
-    </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.2">
+        <v>-87.694647</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12">
       <c r="A65">
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C65" t="s">
-        <v>54</v>
+        <v>119</v>
       </c>
       <c r="D65" t="s">
-        <v>105</v>
+        <v>177</v>
       </c>
       <c r="E65" t="s">
-        <v>135</v>
+        <v>260</v>
       </c>
       <c r="F65" t="s">
-        <v>138</v>
+        <v>322</v>
       </c>
       <c r="G65">
         <v>1927</v>
@@ -3407,33 +3991,33 @@
         <v>1</v>
       </c>
       <c r="J65" s="2" t="s">
-        <v>196</v>
+        <v>380</v>
       </c>
       <c r="K65">
-        <v>41.896086199999999</v>
+        <v>41.8960862</v>
       </c>
       <c r="L65">
-        <v>-87.671374599999993</v>
-      </c>
-    </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.2">
+        <v>-87.67137459999999</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12">
       <c r="A66">
         <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="C66" t="s">
-        <v>69</v>
+        <v>134</v>
       </c>
       <c r="D66" t="s">
-        <v>106</v>
+        <v>178</v>
       </c>
       <c r="E66" t="s">
-        <v>208</v>
+        <v>261</v>
       </c>
       <c r="F66" t="s">
-        <v>138</v>
+        <v>322</v>
       </c>
       <c r="G66">
         <v>1927</v>
@@ -3445,33 +4029,33 @@
         <v>1</v>
       </c>
       <c r="J66" s="2" t="s">
-        <v>197</v>
+        <v>381</v>
       </c>
       <c r="K66">
-        <v>41.797837399999999</v>
+        <v>41.7978374</v>
       </c>
       <c r="L66">
-        <v>-87.629691100000002</v>
-      </c>
-    </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.2">
+        <v>-87.6296911</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12">
       <c r="A67">
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="C67" t="s">
-        <v>59</v>
+        <v>124</v>
       </c>
       <c r="D67" t="s">
-        <v>107</v>
+        <v>179</v>
       </c>
       <c r="E67" t="s">
-        <v>136</v>
+        <v>262</v>
       </c>
       <c r="F67" t="s">
-        <v>138</v>
+        <v>322</v>
       </c>
       <c r="G67">
         <v>1927</v>
@@ -3483,33 +4067,33 @@
         <v>1</v>
       </c>
       <c r="J67" s="2" t="s">
-        <v>198</v>
+        <v>382</v>
       </c>
       <c r="K67">
-        <v>41.904845600000002</v>
+        <v>41.9048456</v>
       </c>
       <c r="L67">
-        <v>-87.677802999999997</v>
-      </c>
-    </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.2">
+        <v>-87.677803</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12">
       <c r="A68">
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="C68" t="s">
-        <v>70</v>
+        <v>135</v>
       </c>
       <c r="D68" t="s">
-        <v>108</v>
+        <v>180</v>
       </c>
       <c r="E68" t="s">
-        <v>137</v>
+        <v>263</v>
       </c>
       <c r="F68" t="s">
-        <v>138</v>
+        <v>322</v>
       </c>
       <c r="G68">
         <v>1927</v>
@@ -3521,33 +4105,33 @@
         <v>1</v>
       </c>
       <c r="J68" s="2" t="s">
-        <v>199</v>
+        <v>383</v>
       </c>
       <c r="K68">
-        <v>41.852747299999997</v>
+        <v>41.8527473</v>
       </c>
       <c r="L68">
-        <v>-87.699008000000006</v>
-      </c>
-    </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.2">
+        <v>-87.69900800000001</v>
+      </c>
+    </row>
+    <row r="69" spans="1:12">
       <c r="A69">
         <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="C69" t="s">
-        <v>66</v>
+        <v>131</v>
       </c>
       <c r="D69" t="s">
-        <v>109</v>
+        <v>181</v>
       </c>
       <c r="E69" t="s">
-        <v>131</v>
+        <v>254</v>
       </c>
       <c r="F69" t="s">
-        <v>138</v>
+        <v>322</v>
       </c>
       <c r="G69">
         <v>1927</v>
@@ -3559,33 +4143,33 @@
         <v>1</v>
       </c>
       <c r="J69" s="2" t="s">
-        <v>200</v>
+        <v>384</v>
       </c>
       <c r="K69">
         <v>41.7030776</v>
       </c>
       <c r="L69">
-        <v>-87.604604199999997</v>
-      </c>
-    </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.2">
+        <v>-87.6046042</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12">
       <c r="A70">
         <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="C70" t="s">
-        <v>66</v>
+        <v>131</v>
       </c>
       <c r="D70" t="s">
-        <v>110</v>
+        <v>182</v>
       </c>
       <c r="E70" t="s">
-        <v>131</v>
+        <v>254</v>
       </c>
       <c r="F70" t="s">
-        <v>138</v>
+        <v>322</v>
       </c>
       <c r="G70">
         <v>1927</v>
@@ -3597,190 +4181,2491 @@
         <v>1</v>
       </c>
       <c r="J70" s="2" t="s">
-        <v>201</v>
+        <v>385</v>
       </c>
       <c r="K70">
-        <v>38.601374300000003</v>
+        <v>41.9281093255862</v>
       </c>
       <c r="L70">
-        <v>-90.073475200000004</v>
-      </c>
-    </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.2">
+        <v>-87.81027788314999</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12">
       <c r="A71">
         <v>70</v>
       </c>
+      <c r="B71" t="s">
+        <v>45</v>
+      </c>
+      <c r="C71" t="s">
+        <v>119</v>
+      </c>
+      <c r="D71" t="s">
+        <v>183</v>
+      </c>
+      <c r="E71" t="s">
+        <v>241</v>
+      </c>
+      <c r="F71" t="s">
+        <v>322</v>
+      </c>
+      <c r="G71">
+        <v>1927</v>
+      </c>
+      <c r="H71">
+        <v>4</v>
+      </c>
+      <c r="I71">
+        <v>1</v>
+      </c>
       <c r="J71" s="2" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.2">
+        <v>386</v>
+      </c>
+      <c r="K71">
+        <v>41.8640642</v>
+      </c>
+      <c r="L71">
+        <v>-87.6469388</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12">
       <c r="A72">
         <v>71</v>
       </c>
-    </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B72" t="s">
+        <v>58</v>
+      </c>
+      <c r="C72" t="s">
+        <v>119</v>
+      </c>
+      <c r="D72" t="s">
+        <v>184</v>
+      </c>
+      <c r="E72" t="s">
+        <v>264</v>
+      </c>
+      <c r="F72" t="s">
+        <v>322</v>
+      </c>
+      <c r="G72">
+        <v>1927</v>
+      </c>
+      <c r="H72">
+        <v>4</v>
+      </c>
+      <c r="I72">
+        <v>1</v>
+      </c>
+      <c r="J72" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="K72">
+        <v>41.8573295</v>
+      </c>
+      <c r="L72">
+        <v>-87.66119399999999</v>
+      </c>
+    </row>
+    <row r="73" spans="1:12">
       <c r="A73">
         <v>72</v>
       </c>
-    </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B73" t="s">
+        <v>59</v>
+      </c>
+      <c r="C73" t="s">
+        <v>119</v>
+      </c>
+      <c r="D73" t="s">
+        <v>155</v>
+      </c>
+      <c r="E73" t="s">
+        <v>265</v>
+      </c>
+      <c r="F73" t="s">
+        <v>322</v>
+      </c>
+      <c r="G73">
+        <v>1927</v>
+      </c>
+      <c r="H73">
+        <v>4</v>
+      </c>
+      <c r="I73">
+        <v>1</v>
+      </c>
+      <c r="J73" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="K73">
+        <v>41.9294291</v>
+      </c>
+      <c r="L73">
+        <v>-87.8088834</v>
+      </c>
+    </row>
+    <row r="74" spans="1:12">
       <c r="A74">
         <v>73</v>
       </c>
-    </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B74" t="s">
+        <v>60</v>
+      </c>
+      <c r="C74" t="s">
+        <v>136</v>
+      </c>
+      <c r="D74" t="s">
+        <v>185</v>
+      </c>
+      <c r="E74" t="s">
+        <v>266</v>
+      </c>
+      <c r="F74" t="s">
+        <v>322</v>
+      </c>
+      <c r="G74">
+        <v>1927</v>
+      </c>
+      <c r="H74">
+        <v>4</v>
+      </c>
+      <c r="I74">
+        <v>1</v>
+      </c>
+      <c r="J74" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="K74">
+        <v>41.8822694</v>
+      </c>
+      <c r="L74">
+        <v>-87.6472661</v>
+      </c>
+    </row>
+    <row r="75" spans="1:12">
       <c r="A75">
         <v>74</v>
       </c>
-    </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B75" t="s">
+        <v>61</v>
+      </c>
+      <c r="C75" t="s">
+        <v>136</v>
+      </c>
+      <c r="D75" t="s">
+        <v>186</v>
+      </c>
+      <c r="E75" t="s">
+        <v>267</v>
+      </c>
+      <c r="F75" t="s">
+        <v>322</v>
+      </c>
+      <c r="G75">
+        <v>1927</v>
+      </c>
+      <c r="H75">
+        <v>4</v>
+      </c>
+      <c r="I75">
+        <v>1</v>
+      </c>
+      <c r="J75" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="K75">
+        <v>41.9714311</v>
+      </c>
+      <c r="L75">
+        <v>-87.7495246</v>
+      </c>
+    </row>
+    <row r="76" spans="1:12">
       <c r="A76">
         <v>75</v>
       </c>
-    </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B76" t="s">
+        <v>62</v>
+      </c>
+      <c r="C76" t="s">
+        <v>136</v>
+      </c>
+      <c r="D76" t="s">
+        <v>187</v>
+      </c>
+      <c r="E76" t="s">
+        <v>268</v>
+      </c>
+      <c r="F76" t="s">
+        <v>322</v>
+      </c>
+      <c r="G76">
+        <v>1927</v>
+      </c>
+      <c r="H76">
+        <v>4</v>
+      </c>
+      <c r="I76">
+        <v>1</v>
+      </c>
+      <c r="J76" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="K76">
+        <v>41.9016502</v>
+      </c>
+      <c r="L76">
+        <v>-87.6848011</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12">
       <c r="A77">
         <v>76</v>
       </c>
-    </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B77" t="s">
+        <v>63</v>
+      </c>
+      <c r="C77" t="s">
+        <v>137</v>
+      </c>
+      <c r="D77" t="s">
+        <v>188</v>
+      </c>
+      <c r="E77" t="s">
+        <v>269</v>
+      </c>
+      <c r="F77" t="s">
+        <v>322</v>
+      </c>
+      <c r="G77">
+        <v>1927</v>
+      </c>
+      <c r="H77">
+        <v>4</v>
+      </c>
+      <c r="I77">
+        <v>1</v>
+      </c>
+      <c r="J77" s="2" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12">
       <c r="A78">
         <v>77</v>
       </c>
-    </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B78" t="s">
+        <v>64</v>
+      </c>
+      <c r="C78" t="s">
+        <v>134</v>
+      </c>
+      <c r="D78" t="s">
+        <v>189</v>
+      </c>
+      <c r="E78" t="s">
+        <v>270</v>
+      </c>
+      <c r="F78" t="s">
+        <v>322</v>
+      </c>
+      <c r="G78">
+        <v>1927</v>
+      </c>
+      <c r="H78">
+        <v>4</v>
+      </c>
+      <c r="I78">
+        <v>1</v>
+      </c>
+      <c r="J78" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="K78">
+        <v>41.9036227</v>
+      </c>
+      <c r="L78">
+        <v>-87.665217</v>
+      </c>
+    </row>
+    <row r="79" spans="1:12">
       <c r="A79">
         <v>78</v>
       </c>
-    </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B79" t="s">
+        <v>53</v>
+      </c>
+      <c r="C79" t="s">
+        <v>134</v>
+      </c>
+      <c r="D79" t="s">
+        <v>190</v>
+      </c>
+      <c r="E79" t="s">
+        <v>271</v>
+      </c>
+      <c r="F79" t="s">
+        <v>322</v>
+      </c>
+      <c r="G79">
+        <v>1927</v>
+      </c>
+      <c r="H79">
+        <v>4</v>
+      </c>
+      <c r="I79">
+        <v>1</v>
+      </c>
+      <c r="J79" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="K79">
+        <v>41.7978374</v>
+      </c>
+      <c r="L79">
+        <v>-87.6296911</v>
+      </c>
+    </row>
+    <row r="80" spans="1:12">
       <c r="A80">
         <v>79</v>
       </c>
-    </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B80" t="s">
+        <v>65</v>
+      </c>
+      <c r="C80" t="s">
+        <v>127</v>
+      </c>
+      <c r="D80" t="s">
+        <v>191</v>
+      </c>
+      <c r="E80" t="s">
+        <v>191</v>
+      </c>
+      <c r="F80" t="s">
+        <v>322</v>
+      </c>
+      <c r="G80">
+        <v>1927</v>
+      </c>
+      <c r="H80">
+        <v>4</v>
+      </c>
+      <c r="I80">
+        <v>1</v>
+      </c>
+      <c r="J80" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="K80">
+        <v>41.591706</v>
+      </c>
+      <c r="L80">
+        <v>-87.34155579999999</v>
+      </c>
+    </row>
+    <row r="81" spans="1:12">
       <c r="A81">
         <v>80</v>
       </c>
-    </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B81" t="s">
+        <v>66</v>
+      </c>
+      <c r="C81" t="s">
+        <v>127</v>
+      </c>
+      <c r="D81" t="s">
+        <v>192</v>
+      </c>
+      <c r="E81" t="s">
+        <v>272</v>
+      </c>
+      <c r="F81" t="s">
+        <v>322</v>
+      </c>
+      <c r="G81">
+        <v>1927</v>
+      </c>
+      <c r="H81">
+        <v>4</v>
+      </c>
+      <c r="I81">
+        <v>1</v>
+      </c>
+      <c r="J81" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="K81">
+        <v>41.8121376</v>
+      </c>
+      <c r="L81">
+        <v>-87.66720429999999</v>
+      </c>
+    </row>
+    <row r="82" spans="1:12">
       <c r="A82">
         <v>81</v>
       </c>
-    </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B82" t="s">
+        <v>67</v>
+      </c>
+      <c r="C82" t="s">
+        <v>131</v>
+      </c>
+      <c r="D82" t="s">
+        <v>193</v>
+      </c>
+      <c r="E82" t="s">
+        <v>273</v>
+      </c>
+      <c r="F82" t="s">
+        <v>322</v>
+      </c>
+      <c r="G82">
+        <v>1927</v>
+      </c>
+      <c r="H82">
+        <v>4</v>
+      </c>
+      <c r="I82">
+        <v>1</v>
+      </c>
+      <c r="J82" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="K82">
+        <v>41.8747708</v>
+      </c>
+      <c r="L82">
+        <v>-87.6294944</v>
+      </c>
+    </row>
+    <row r="83" spans="1:12">
       <c r="A83">
         <v>82</v>
       </c>
-    </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B83" t="s">
+        <v>31</v>
+      </c>
+      <c r="C83" t="s">
+        <v>138</v>
+      </c>
+      <c r="D83" t="s">
+        <v>194</v>
+      </c>
+      <c r="E83" t="s">
+        <v>274</v>
+      </c>
+      <c r="F83" t="s">
+        <v>322</v>
+      </c>
+      <c r="G83">
+        <v>1927</v>
+      </c>
+      <c r="H83">
+        <v>5</v>
+      </c>
+      <c r="I83">
+        <v>2</v>
+      </c>
+      <c r="K83">
+        <v>41.8960862</v>
+      </c>
+      <c r="L83">
+        <v>-87.67137459999999</v>
+      </c>
+    </row>
+    <row r="84" spans="1:12">
       <c r="A84">
         <v>83</v>
       </c>
-    </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B84" t="s">
+        <v>68</v>
+      </c>
+      <c r="C84" t="s">
+        <v>134</v>
+      </c>
+      <c r="D84" t="s">
+        <v>186</v>
+      </c>
+      <c r="E84" t="s">
+        <v>275</v>
+      </c>
+      <c r="F84" t="s">
+        <v>322</v>
+      </c>
+      <c r="G84">
+        <v>1927</v>
+      </c>
+      <c r="H84">
+        <v>5</v>
+      </c>
+      <c r="I84">
+        <v>2</v>
+      </c>
+      <c r="K84">
+        <v>41.8657386</v>
+      </c>
+      <c r="L84">
+        <v>-87.7425053</v>
+      </c>
+    </row>
+    <row r="85" spans="1:12">
       <c r="A85">
         <v>84</v>
       </c>
-    </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B85" t="s">
+        <v>69</v>
+      </c>
+      <c r="C85" t="s">
+        <v>134</v>
+      </c>
+      <c r="D85" t="s">
+        <v>195</v>
+      </c>
+      <c r="E85" t="s">
+        <v>276</v>
+      </c>
+      <c r="F85" t="s">
+        <v>322</v>
+      </c>
+      <c r="G85">
+        <v>1927</v>
+      </c>
+      <c r="H85">
+        <v>5</v>
+      </c>
+      <c r="I85">
+        <v>2</v>
+      </c>
+      <c r="K85">
+        <v>41.8804466</v>
+      </c>
+      <c r="L85">
+        <v>-87.7455619</v>
+      </c>
+    </row>
+    <row r="86" spans="1:12">
       <c r="A86">
         <v>85</v>
       </c>
-    </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B86" t="s">
+        <v>70</v>
+      </c>
+      <c r="C86" t="s">
+        <v>124</v>
+      </c>
+      <c r="D86" t="s">
+        <v>196</v>
+      </c>
+      <c r="E86" t="s">
+        <v>277</v>
+      </c>
+      <c r="F86" t="s">
+        <v>322</v>
+      </c>
+      <c r="G86">
+        <v>1927</v>
+      </c>
+      <c r="H86">
+        <v>5</v>
+      </c>
+      <c r="I86">
+        <v>2</v>
+      </c>
+      <c r="K86">
+        <v>41.8985404</v>
+      </c>
+      <c r="L86">
+        <v>-87.6878342</v>
+      </c>
+    </row>
+    <row r="87" spans="1:12">
       <c r="A87">
         <v>86</v>
       </c>
-    </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B87" t="s">
+        <v>71</v>
+      </c>
+      <c r="C87" t="s">
+        <v>119</v>
+      </c>
+      <c r="D87" t="s">
+        <v>197</v>
+      </c>
+      <c r="E87" t="s">
+        <v>264</v>
+      </c>
+      <c r="F87" t="s">
+        <v>322</v>
+      </c>
+      <c r="G87">
+        <v>1927</v>
+      </c>
+      <c r="H87">
+        <v>6</v>
+      </c>
+      <c r="I87">
+        <v>1</v>
+      </c>
+      <c r="K87">
+        <v>41.8853195</v>
+      </c>
+      <c r="L87">
+        <v>-87.6282971</v>
+      </c>
+    </row>
+    <row r="88" spans="1:12">
       <c r="A88">
         <v>87</v>
       </c>
-    </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B88" t="s">
+        <v>72</v>
+      </c>
+      <c r="C88" t="s">
+        <v>119</v>
+      </c>
+      <c r="D88" t="s">
+        <v>198</v>
+      </c>
+      <c r="E88" t="s">
+        <v>278</v>
+      </c>
+      <c r="F88" t="s">
+        <v>322</v>
+      </c>
+      <c r="G88">
+        <v>1927</v>
+      </c>
+      <c r="H88">
+        <v>6</v>
+      </c>
+      <c r="I88">
+        <v>1</v>
+      </c>
+      <c r="K88">
+        <v>41.8829547</v>
+      </c>
+      <c r="L88">
+        <v>-87.6340866</v>
+      </c>
+    </row>
+    <row r="89" spans="1:12">
       <c r="A89">
         <v>88</v>
       </c>
-    </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B89" t="s">
+        <v>73</v>
+      </c>
+      <c r="C89" t="s">
+        <v>119</v>
+      </c>
+      <c r="D89" t="s">
+        <v>199</v>
+      </c>
+      <c r="E89" t="s">
+        <v>279</v>
+      </c>
+      <c r="F89" t="s">
+        <v>322</v>
+      </c>
+      <c r="G89">
+        <v>1927</v>
+      </c>
+      <c r="H89">
+        <v>6</v>
+      </c>
+      <c r="I89">
+        <v>1</v>
+      </c>
+      <c r="K89">
+        <v>41.9266193</v>
+      </c>
+      <c r="L89">
+        <v>-87.6893286</v>
+      </c>
+    </row>
+    <row r="90" spans="1:12">
       <c r="A90">
         <v>89</v>
       </c>
+      <c r="B90" t="s">
+        <v>74</v>
+      </c>
+      <c r="C90" t="s">
+        <v>123</v>
+      </c>
+      <c r="D90" t="s">
+        <v>186</v>
+      </c>
+      <c r="E90" t="s">
+        <v>280</v>
+      </c>
+      <c r="F90" t="s">
+        <v>322</v>
+      </c>
+      <c r="G90">
+        <v>1927</v>
+      </c>
+      <c r="H90">
+        <v>6</v>
+      </c>
+      <c r="I90">
+        <v>1</v>
+      </c>
+      <c r="K90">
+        <v>41.8931547</v>
+      </c>
+      <c r="L90">
+        <v>-87.6649455</v>
+      </c>
+    </row>
+    <row r="91" spans="1:12">
+      <c r="A91">
+        <v>90</v>
+      </c>
+      <c r="B91" t="s">
+        <v>75</v>
+      </c>
+      <c r="C91" t="s">
+        <v>134</v>
+      </c>
+      <c r="D91" t="s">
+        <v>200</v>
+      </c>
+      <c r="E91" t="s">
+        <v>281</v>
+      </c>
+      <c r="F91" t="s">
+        <v>322</v>
+      </c>
+      <c r="G91">
+        <v>1927</v>
+      </c>
+      <c r="H91">
+        <v>6</v>
+      </c>
+      <c r="I91">
+        <v>1</v>
+      </c>
+      <c r="K91">
+        <v>41.8815396</v>
+      </c>
+      <c r="L91">
+        <v>-87.6307583</v>
+      </c>
+    </row>
+    <row r="92" spans="1:12">
+      <c r="A92">
+        <v>91</v>
+      </c>
+      <c r="B92" t="s">
+        <v>76</v>
+      </c>
+      <c r="C92" t="s">
+        <v>136</v>
+      </c>
+      <c r="D92" t="s">
+        <v>186</v>
+      </c>
+      <c r="E92" t="s">
+        <v>282</v>
+      </c>
+      <c r="F92" t="s">
+        <v>322</v>
+      </c>
+      <c r="G92">
+        <v>1927</v>
+      </c>
+      <c r="H92">
+        <v>6</v>
+      </c>
+      <c r="I92">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93" spans="1:12">
+      <c r="A93">
+        <v>92</v>
+      </c>
+      <c r="B93" t="s">
+        <v>77</v>
+      </c>
+      <c r="C93" t="s">
+        <v>131</v>
+      </c>
+      <c r="D93" t="s">
+        <v>201</v>
+      </c>
+      <c r="E93" t="s">
+        <v>283</v>
+      </c>
+      <c r="F93" t="s">
+        <v>322</v>
+      </c>
+      <c r="G93">
+        <v>1927</v>
+      </c>
+      <c r="H93">
+        <v>6</v>
+      </c>
+      <c r="I93">
+        <v>1</v>
+      </c>
+      <c r="K93">
+        <v>41.858444</v>
+      </c>
+      <c r="L93">
+        <v>-87.69348720000001</v>
+      </c>
+    </row>
+    <row r="94" spans="1:12">
+      <c r="A94">
+        <v>93</v>
+      </c>
+      <c r="B94" t="s">
+        <v>78</v>
+      </c>
+      <c r="C94" t="s">
+        <v>139</v>
+      </c>
+      <c r="D94" t="s">
+        <v>202</v>
+      </c>
+      <c r="E94" t="s">
+        <v>284</v>
+      </c>
+      <c r="F94" t="s">
+        <v>322</v>
+      </c>
+      <c r="G94">
+        <v>1927</v>
+      </c>
+      <c r="H94">
+        <v>6</v>
+      </c>
+      <c r="I94">
+        <v>1</v>
+      </c>
+      <c r="K94">
+        <v>41.8664424</v>
+      </c>
+      <c r="L94">
+        <v>-87.70961800000001</v>
+      </c>
+    </row>
+    <row r="95" spans="1:12">
+      <c r="A95">
+        <v>94</v>
+      </c>
+      <c r="B95" t="s">
+        <v>79</v>
+      </c>
+      <c r="C95" t="s">
+        <v>131</v>
+      </c>
+      <c r="D95" t="s">
+        <v>203</v>
+      </c>
+      <c r="E95" t="s">
+        <v>285</v>
+      </c>
+      <c r="F95" t="s">
+        <v>322</v>
+      </c>
+      <c r="G95">
+        <v>1927</v>
+      </c>
+      <c r="H95">
+        <v>7</v>
+      </c>
+      <c r="I95">
+        <v>1</v>
+      </c>
+      <c r="K95">
+        <v>41.801038</v>
+      </c>
+      <c r="L95">
+        <v>-87.6737224</v>
+      </c>
+    </row>
+    <row r="96" spans="1:12">
+      <c r="A96">
+        <v>95</v>
+      </c>
+      <c r="B96" t="s">
+        <v>80</v>
+      </c>
+      <c r="C96" t="s">
+        <v>119</v>
+      </c>
+      <c r="D96" t="s">
+        <v>204</v>
+      </c>
+      <c r="E96" t="s">
+        <v>286</v>
+      </c>
+      <c r="F96" t="s">
+        <v>322</v>
+      </c>
+      <c r="G96">
+        <v>1927</v>
+      </c>
+      <c r="H96">
+        <v>7</v>
+      </c>
+      <c r="I96">
+        <v>1</v>
+      </c>
+      <c r="K96">
+        <v>41.5095962</v>
+      </c>
+      <c r="L96">
+        <v>-87.6600238</v>
+      </c>
+    </row>
+    <row r="97" spans="1:12">
+      <c r="A97">
+        <v>96</v>
+      </c>
+      <c r="B97" t="s">
+        <v>81</v>
+      </c>
+      <c r="C97" t="s">
+        <v>119</v>
+      </c>
+      <c r="D97" t="s">
+        <v>205</v>
+      </c>
+      <c r="E97" t="s">
+        <v>286</v>
+      </c>
+      <c r="F97" t="s">
+        <v>322</v>
+      </c>
+      <c r="G97">
+        <v>1927</v>
+      </c>
+      <c r="H97">
+        <v>7</v>
+      </c>
+      <c r="I97">
+        <v>1</v>
+      </c>
+      <c r="K97">
+        <v>41.8663979</v>
+      </c>
+      <c r="L97">
+        <v>-87.7133211</v>
+      </c>
+    </row>
+    <row r="98" spans="1:12">
+      <c r="A98">
+        <v>97</v>
+      </c>
+      <c r="B98" t="s">
+        <v>82</v>
+      </c>
+      <c r="C98" t="s">
+        <v>119</v>
+      </c>
+      <c r="D98" t="s">
+        <v>206</v>
+      </c>
+      <c r="E98" t="s">
+        <v>287</v>
+      </c>
+      <c r="F98" t="s">
+        <v>322</v>
+      </c>
+      <c r="G98">
+        <v>1927</v>
+      </c>
+      <c r="H98">
+        <v>7</v>
+      </c>
+      <c r="I98">
+        <v>1</v>
+      </c>
+      <c r="K98">
+        <v>41.9170918</v>
+      </c>
+      <c r="L98">
+        <v>-87.68801620000001</v>
+      </c>
+    </row>
+    <row r="99" spans="1:12">
+      <c r="A99">
+        <v>98</v>
+      </c>
+      <c r="B99" t="s">
+        <v>83</v>
+      </c>
+      <c r="C99" t="s">
+        <v>123</v>
+      </c>
+      <c r="D99" t="s">
+        <v>186</v>
+      </c>
+      <c r="E99" t="s">
+        <v>288</v>
+      </c>
+      <c r="F99" t="s">
+        <v>322</v>
+      </c>
+      <c r="G99">
+        <v>1927</v>
+      </c>
+      <c r="H99">
+        <v>7</v>
+      </c>
+      <c r="I99">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:12">
+      <c r="A100">
+        <v>99</v>
+      </c>
+      <c r="B100" t="s">
+        <v>84</v>
+      </c>
+      <c r="C100" t="s">
+        <v>123</v>
+      </c>
+      <c r="D100" t="s">
+        <v>207</v>
+      </c>
+      <c r="E100" t="s">
+        <v>289</v>
+      </c>
+      <c r="F100" t="s">
+        <v>322</v>
+      </c>
+      <c r="G100">
+        <v>1927</v>
+      </c>
+      <c r="H100">
+        <v>7</v>
+      </c>
+      <c r="I100">
+        <v>1</v>
+      </c>
+      <c r="K100">
+        <v>41.9183087</v>
+      </c>
+      <c r="L100">
+        <v>-87.6828014</v>
+      </c>
+    </row>
+    <row r="101" spans="1:12">
+      <c r="A101">
+        <v>100</v>
+      </c>
+      <c r="B101" t="s">
+        <v>85</v>
+      </c>
+      <c r="C101" t="s">
+        <v>122</v>
+      </c>
+      <c r="D101" t="s">
+        <v>186</v>
+      </c>
+      <c r="E101" t="s">
+        <v>290</v>
+      </c>
+      <c r="F101" t="s">
+        <v>322</v>
+      </c>
+      <c r="G101">
+        <v>1927</v>
+      </c>
+      <c r="H101">
+        <v>7</v>
+      </c>
+      <c r="I101">
+        <v>1</v>
+      </c>
+      <c r="K101">
+        <v>41.8530185</v>
+      </c>
+      <c r="L101">
+        <v>-87.64590889999999</v>
+      </c>
+    </row>
+    <row r="102" spans="1:12">
+      <c r="A102">
+        <v>101</v>
+      </c>
+      <c r="B102" t="s">
+        <v>86</v>
+      </c>
+      <c r="C102" t="s">
+        <v>120</v>
+      </c>
+      <c r="D102" t="s">
+        <v>208</v>
+      </c>
+      <c r="E102" t="s">
+        <v>291</v>
+      </c>
+      <c r="F102" t="s">
+        <v>322</v>
+      </c>
+      <c r="G102">
+        <v>1927</v>
+      </c>
+      <c r="H102">
+        <v>7</v>
+      </c>
+      <c r="I102">
+        <v>1</v>
+      </c>
+      <c r="K102">
+        <v>41.895854</v>
+      </c>
+      <c r="L102">
+        <v>-87.68512610000001</v>
+      </c>
+    </row>
+    <row r="103" spans="1:12">
+      <c r="A103">
+        <v>102</v>
+      </c>
+      <c r="B103" t="s">
+        <v>87</v>
+      </c>
+      <c r="C103" t="s">
+        <v>132</v>
+      </c>
+      <c r="D103" t="s">
+        <v>209</v>
+      </c>
+      <c r="E103" t="s">
+        <v>292</v>
+      </c>
+      <c r="F103" t="s">
+        <v>322</v>
+      </c>
+      <c r="G103">
+        <v>1927</v>
+      </c>
+      <c r="H103">
+        <v>8</v>
+      </c>
+      <c r="I103">
+        <v>1</v>
+      </c>
+      <c r="K103">
+        <v>41.8543643</v>
+      </c>
+      <c r="L103">
+        <v>-87.7052173</v>
+      </c>
+    </row>
+    <row r="104" spans="1:12">
+      <c r="A104">
+        <v>103</v>
+      </c>
+      <c r="B104" t="s">
+        <v>88</v>
+      </c>
+      <c r="C104" t="s">
+        <v>125</v>
+      </c>
+      <c r="D104" t="s">
+        <v>210</v>
+      </c>
+      <c r="E104" t="s">
+        <v>293</v>
+      </c>
+      <c r="F104" t="s">
+        <v>322</v>
+      </c>
+      <c r="G104">
+        <v>1927</v>
+      </c>
+      <c r="H104">
+        <v>9</v>
+      </c>
+      <c r="I104">
+        <v>1</v>
+      </c>
+      <c r="K104">
+        <v>41.9101667</v>
+      </c>
+      <c r="L104">
+        <v>-87.6948196</v>
+      </c>
+    </row>
+    <row r="105" spans="1:12">
+      <c r="A105">
+        <v>104</v>
+      </c>
+      <c r="B105" t="s">
+        <v>89</v>
+      </c>
+      <c r="C105" t="s">
+        <v>134</v>
+      </c>
+      <c r="D105" t="s">
+        <v>211</v>
+      </c>
+      <c r="E105" t="s">
+        <v>294</v>
+      </c>
+      <c r="F105" t="s">
+        <v>322</v>
+      </c>
+      <c r="G105">
+        <v>1927</v>
+      </c>
+      <c r="H105">
+        <v>9</v>
+      </c>
+      <c r="I105">
+        <v>1</v>
+      </c>
+      <c r="K105">
+        <v>41.9019727</v>
+      </c>
+      <c r="L105">
+        <v>-87.6713489</v>
+      </c>
+    </row>
+    <row r="106" spans="1:12">
+      <c r="A106">
+        <v>105</v>
+      </c>
+      <c r="B106" t="s">
+        <v>90</v>
+      </c>
+      <c r="C106" t="s">
+        <v>122</v>
+      </c>
+      <c r="D106" t="s">
+        <v>186</v>
+      </c>
+      <c r="E106" t="s">
+        <v>295</v>
+      </c>
+      <c r="F106" t="s">
+        <v>322</v>
+      </c>
+      <c r="G106">
+        <v>1927</v>
+      </c>
+      <c r="H106">
+        <v>9</v>
+      </c>
+      <c r="I106">
+        <v>1</v>
+      </c>
+      <c r="K106">
+        <v>41.8577481</v>
+      </c>
+      <c r="L106">
+        <v>-87.63398650000001</v>
+      </c>
+    </row>
+    <row r="107" spans="1:12">
+      <c r="A107">
+        <v>106</v>
+      </c>
+      <c r="B107" t="s">
+        <v>91</v>
+      </c>
+      <c r="C107" t="s">
+        <v>122</v>
+      </c>
+      <c r="D107" t="s">
+        <v>186</v>
+      </c>
+      <c r="E107" t="s">
+        <v>296</v>
+      </c>
+      <c r="F107" t="s">
+        <v>322</v>
+      </c>
+      <c r="G107">
+        <v>1927</v>
+      </c>
+      <c r="H107">
+        <v>9</v>
+      </c>
+      <c r="I107">
+        <v>1</v>
+      </c>
+      <c r="K107">
+        <v>41.8641815</v>
+      </c>
+      <c r="L107">
+        <v>-87.65084709999999</v>
+      </c>
+    </row>
+    <row r="108" spans="1:12">
+      <c r="A108">
+        <v>107</v>
+      </c>
+      <c r="B108" t="s">
+        <v>92</v>
+      </c>
+      <c r="C108" t="s">
+        <v>122</v>
+      </c>
+      <c r="D108" t="s">
+        <v>186</v>
+      </c>
+      <c r="E108" t="s">
+        <v>297</v>
+      </c>
+      <c r="F108" t="s">
+        <v>322</v>
+      </c>
+      <c r="G108">
+        <v>1927</v>
+      </c>
+      <c r="H108">
+        <v>9</v>
+      </c>
+      <c r="I108">
+        <v>1</v>
+      </c>
+      <c r="K108">
+        <v>41.8626087</v>
+      </c>
+      <c r="L108">
+        <v>-87.69127229999999</v>
+      </c>
+    </row>
+    <row r="109" spans="1:12">
+      <c r="A109">
+        <v>108</v>
+      </c>
+      <c r="B109" t="s">
+        <v>93</v>
+      </c>
+      <c r="C109" t="s">
+        <v>119</v>
+      </c>
+      <c r="D109" t="s">
+        <v>212</v>
+      </c>
+      <c r="E109" t="s">
+        <v>298</v>
+      </c>
+      <c r="F109" t="s">
+        <v>322</v>
+      </c>
+      <c r="G109">
+        <v>1927</v>
+      </c>
+      <c r="H109">
+        <v>10</v>
+      </c>
+      <c r="I109">
+        <v>1</v>
+      </c>
+      <c r="K109">
+        <v>41.8816918</v>
+      </c>
+      <c r="L109">
+        <v>-87.6292825</v>
+      </c>
+    </row>
+    <row r="110" spans="1:12">
+      <c r="A110">
+        <v>109</v>
+      </c>
+      <c r="B110" t="s">
+        <v>94</v>
+      </c>
+      <c r="C110" t="s">
+        <v>119</v>
+      </c>
+      <c r="D110" t="s">
+        <v>213</v>
+      </c>
+      <c r="E110" t="s">
+        <v>299</v>
+      </c>
+      <c r="F110" t="s">
+        <v>322</v>
+      </c>
+      <c r="G110">
+        <v>1927</v>
+      </c>
+      <c r="H110">
+        <v>10</v>
+      </c>
+      <c r="I110">
+        <v>1</v>
+      </c>
+      <c r="K110">
+        <v>41.895534</v>
+      </c>
+      <c r="L110">
+        <v>-87.6830032</v>
+      </c>
+    </row>
+    <row r="111" spans="1:12">
+      <c r="A111">
+        <v>110</v>
+      </c>
+      <c r="B111" t="s">
+        <v>95</v>
+      </c>
+      <c r="C111" t="s">
+        <v>123</v>
+      </c>
+      <c r="D111" t="s">
+        <v>186</v>
+      </c>
+      <c r="E111" t="s">
+        <v>300</v>
+      </c>
+      <c r="F111" t="s">
+        <v>322</v>
+      </c>
+      <c r="G111">
+        <v>1927</v>
+      </c>
+      <c r="H111">
+        <v>10</v>
+      </c>
+      <c r="I111">
+        <v>1</v>
+      </c>
+      <c r="K111">
+        <v>41.8959446</v>
+      </c>
+      <c r="L111">
+        <v>-87.67979769999999</v>
+      </c>
+    </row>
+    <row r="112" spans="1:12">
+      <c r="A112">
+        <v>111</v>
+      </c>
+      <c r="B112" t="s">
+        <v>95</v>
+      </c>
+      <c r="C112" t="s">
+        <v>136</v>
+      </c>
+      <c r="D112" t="s">
+        <v>186</v>
+      </c>
+      <c r="E112" t="s">
+        <v>301</v>
+      </c>
+      <c r="F112" t="s">
+        <v>322</v>
+      </c>
+      <c r="G112">
+        <v>1927</v>
+      </c>
+      <c r="H112">
+        <v>10</v>
+      </c>
+      <c r="I112">
+        <v>1</v>
+      </c>
+      <c r="K112">
+        <v>41.8959446</v>
+      </c>
+      <c r="L112">
+        <v>-87.67979769999999</v>
+      </c>
+    </row>
+    <row r="113" spans="1:12">
+      <c r="A113">
+        <v>112</v>
+      </c>
+      <c r="B113" t="s">
+        <v>31</v>
+      </c>
+      <c r="C113" t="s">
+        <v>123</v>
+      </c>
+      <c r="D113" t="s">
+        <v>186</v>
+      </c>
+      <c r="E113" t="s">
+        <v>302</v>
+      </c>
+      <c r="F113" t="s">
+        <v>322</v>
+      </c>
+      <c r="G113">
+        <v>1927</v>
+      </c>
+      <c r="H113">
+        <v>10</v>
+      </c>
+      <c r="I113">
+        <v>1</v>
+      </c>
+      <c r="K113">
+        <v>41.8960862</v>
+      </c>
+      <c r="L113">
+        <v>-87.67137459999999</v>
+      </c>
+    </row>
+    <row r="114" spans="1:12">
+      <c r="A114">
+        <v>113</v>
+      </c>
+      <c r="B114" t="s">
+        <v>96</v>
+      </c>
+      <c r="C114" t="s">
+        <v>140</v>
+      </c>
+      <c r="D114" t="s">
+        <v>214</v>
+      </c>
+      <c r="E114" t="s">
+        <v>237</v>
+      </c>
+      <c r="F114" t="s">
+        <v>322</v>
+      </c>
+      <c r="G114">
+        <v>1927</v>
+      </c>
+      <c r="H114">
+        <v>10</v>
+      </c>
+      <c r="I114">
+        <v>1</v>
+      </c>
+      <c r="K114">
+        <v>41.8955555</v>
+      </c>
+      <c r="L114">
+        <v>-87.6821922</v>
+      </c>
+    </row>
+    <row r="115" spans="1:12">
+      <c r="A115">
+        <v>114</v>
+      </c>
+      <c r="B115" t="s">
+        <v>97</v>
+      </c>
+      <c r="C115" t="s">
+        <v>138</v>
+      </c>
+      <c r="D115" t="s">
+        <v>215</v>
+      </c>
+      <c r="E115" t="s">
+        <v>303</v>
+      </c>
+      <c r="F115" t="s">
+        <v>322</v>
+      </c>
+      <c r="G115">
+        <v>1927</v>
+      </c>
+      <c r="H115">
+        <v>10</v>
+      </c>
+      <c r="I115">
+        <v>1</v>
+      </c>
+      <c r="K115">
+        <v>40.7549518</v>
+      </c>
+      <c r="L115">
+        <v>-74.16626359999999</v>
+      </c>
+    </row>
+    <row r="116" spans="1:12">
+      <c r="A116">
+        <v>115</v>
+      </c>
+      <c r="B116" t="s">
+        <v>98</v>
+      </c>
+      <c r="C116" t="s">
+        <v>136</v>
+      </c>
+      <c r="D116" t="s">
+        <v>216</v>
+      </c>
+      <c r="E116" t="s">
+        <v>304</v>
+      </c>
+      <c r="F116" t="s">
+        <v>322</v>
+      </c>
+      <c r="G116">
+        <v>1927</v>
+      </c>
+      <c r="H116">
+        <v>10</v>
+      </c>
+      <c r="I116">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="117" spans="1:12">
+      <c r="B117" t="s">
+        <v>99</v>
+      </c>
+      <c r="C117" t="s">
+        <v>138</v>
+      </c>
+      <c r="D117" t="s">
+        <v>217</v>
+      </c>
+      <c r="E117" t="s">
+        <v>305</v>
+      </c>
+      <c r="F117" t="s">
+        <v>322</v>
+      </c>
+      <c r="G117">
+        <v>1927</v>
+      </c>
+      <c r="H117">
+        <v>10</v>
+      </c>
+      <c r="I117">
+        <v>1</v>
+      </c>
+      <c r="K117">
+        <v>41.9006835</v>
+      </c>
+      <c r="L117">
+        <v>-87.6617732</v>
+      </c>
+    </row>
+    <row r="118" spans="1:12">
+      <c r="B118" t="s">
+        <v>100</v>
+      </c>
+      <c r="C118" t="s">
+        <v>132</v>
+      </c>
+      <c r="D118" t="s">
+        <v>218</v>
+      </c>
+      <c r="E118" t="s">
+        <v>306</v>
+      </c>
+      <c r="F118" t="s">
+        <v>322</v>
+      </c>
+      <c r="G118">
+        <v>1927</v>
+      </c>
+      <c r="H118">
+        <v>10</v>
+      </c>
+      <c r="I118">
+        <v>1</v>
+      </c>
+      <c r="K118">
+        <v>41.8574615</v>
+      </c>
+      <c r="L118">
+        <v>-87.6664681</v>
+      </c>
+    </row>
+    <row r="119" spans="1:12">
+      <c r="B119" t="s">
+        <v>101</v>
+      </c>
+      <c r="C119" t="s">
+        <v>122</v>
+      </c>
+      <c r="D119" t="s">
+        <v>186</v>
+      </c>
+      <c r="E119" t="s">
+        <v>307</v>
+      </c>
+      <c r="F119" t="s">
+        <v>322</v>
+      </c>
+      <c r="G119">
+        <v>1927</v>
+      </c>
+      <c r="H119">
+        <v>10</v>
+      </c>
+      <c r="I119">
+        <v>1</v>
+      </c>
+      <c r="K119">
+        <v>41.9029932</v>
+      </c>
+      <c r="L119">
+        <v>-87.67576219999999</v>
+      </c>
+    </row>
+    <row r="120" spans="1:12">
+      <c r="B120" t="s">
+        <v>102</v>
+      </c>
+      <c r="C120" t="s">
+        <v>126</v>
+      </c>
+      <c r="D120" t="s">
+        <v>219</v>
+      </c>
+      <c r="E120" t="s">
+        <v>157</v>
+      </c>
+      <c r="F120" t="s">
+        <v>322</v>
+      </c>
+      <c r="G120">
+        <v>1927</v>
+      </c>
+      <c r="H120">
+        <v>10</v>
+      </c>
+      <c r="I120">
+        <v>1</v>
+      </c>
+      <c r="K120">
+        <v>41.8847559</v>
+      </c>
+      <c r="L120">
+        <v>-87.62957729999999</v>
+      </c>
+    </row>
+    <row r="121" spans="1:12">
+      <c r="B121" t="s">
+        <v>103</v>
+      </c>
+      <c r="C121" t="s">
+        <v>141</v>
+      </c>
+      <c r="D121" t="s">
+        <v>220</v>
+      </c>
+      <c r="E121" t="s">
+        <v>308</v>
+      </c>
+      <c r="F121" t="s">
+        <v>322</v>
+      </c>
+      <c r="G121">
+        <v>1927</v>
+      </c>
+      <c r="H121">
+        <v>10</v>
+      </c>
+      <c r="I121">
+        <v>1</v>
+      </c>
+      <c r="K121">
+        <v>41.8306639</v>
+      </c>
+      <c r="L121">
+        <v>-87.646435</v>
+      </c>
+    </row>
+    <row r="122" spans="1:12">
+      <c r="B122" t="s">
+        <v>104</v>
+      </c>
+      <c r="C122" t="s">
+        <v>126</v>
+      </c>
+      <c r="D122" t="s">
+        <v>221</v>
+      </c>
+      <c r="E122" t="s">
+        <v>157</v>
+      </c>
+      <c r="F122" t="s">
+        <v>322</v>
+      </c>
+      <c r="G122">
+        <v>1927</v>
+      </c>
+      <c r="H122">
+        <v>10</v>
+      </c>
+      <c r="I122">
+        <v>1</v>
+      </c>
+      <c r="K122">
+        <v>41.8965015433095</v>
+      </c>
+      <c r="L122">
+        <v>-87.6697739625109</v>
+      </c>
+    </row>
+    <row r="123" spans="1:12">
+      <c r="B123" t="s">
+        <v>105</v>
+      </c>
+      <c r="C123" t="s">
+        <v>124</v>
+      </c>
+      <c r="D123" t="s">
+        <v>222</v>
+      </c>
+      <c r="E123" t="s">
+        <v>309</v>
+      </c>
+      <c r="F123" t="s">
+        <v>322</v>
+      </c>
+      <c r="G123">
+        <v>1927</v>
+      </c>
+      <c r="H123">
+        <v>10</v>
+      </c>
+      <c r="I123">
+        <v>1</v>
+      </c>
+      <c r="K123">
+        <v>41.9443208</v>
+      </c>
+      <c r="L123">
+        <v>-87.72337810000001</v>
+      </c>
+    </row>
+    <row r="124" spans="1:12">
+      <c r="B124" t="s">
+        <v>106</v>
+      </c>
+      <c r="C124" t="s">
+        <v>124</v>
+      </c>
+      <c r="D124" t="s">
+        <v>223</v>
+      </c>
+      <c r="E124" t="s">
+        <v>310</v>
+      </c>
+      <c r="F124" t="s">
+        <v>322</v>
+      </c>
+      <c r="G124">
+        <v>1927</v>
+      </c>
+      <c r="H124">
+        <v>10</v>
+      </c>
+      <c r="I124">
+        <v>1</v>
+      </c>
+      <c r="K124">
+        <v>41.9385053</v>
+      </c>
+      <c r="L124">
+        <v>-87.7654883</v>
+      </c>
+    </row>
+    <row r="125" spans="1:12">
+      <c r="B125" t="s">
+        <v>107</v>
+      </c>
+      <c r="C125" t="s">
+        <v>119</v>
+      </c>
+      <c r="D125" t="s">
+        <v>224</v>
+      </c>
+      <c r="E125" t="s">
+        <v>311</v>
+      </c>
+      <c r="F125" t="s">
+        <v>322</v>
+      </c>
+      <c r="G125">
+        <v>1927</v>
+      </c>
+      <c r="H125">
+        <v>11</v>
+      </c>
+      <c r="I125">
+        <v>1</v>
+      </c>
+      <c r="K125">
+        <v>41.8664976</v>
+      </c>
+      <c r="L125">
+        <v>-87.7050874</v>
+      </c>
+    </row>
+    <row r="126" spans="1:12">
+      <c r="B126" t="s">
+        <v>107</v>
+      </c>
+      <c r="C126" t="s">
+        <v>119</v>
+      </c>
+      <c r="D126" t="s">
+        <v>225</v>
+      </c>
+      <c r="E126" t="s">
+        <v>241</v>
+      </c>
+      <c r="F126" t="s">
+        <v>322</v>
+      </c>
+      <c r="G126">
+        <v>1927</v>
+      </c>
+      <c r="H126">
+        <v>11</v>
+      </c>
+      <c r="I126">
+        <v>1</v>
+      </c>
+      <c r="K126">
+        <v>41.8664976</v>
+      </c>
+      <c r="L126">
+        <v>-87.7050874</v>
+      </c>
+    </row>
+    <row r="127" spans="1:12">
+      <c r="B127" t="s">
+        <v>22</v>
+      </c>
+      <c r="C127" t="s">
+        <v>119</v>
+      </c>
+      <c r="D127" t="s">
+        <v>226</v>
+      </c>
+      <c r="E127" t="s">
+        <v>241</v>
+      </c>
+      <c r="F127" t="s">
+        <v>322</v>
+      </c>
+      <c r="G127">
+        <v>1927</v>
+      </c>
+      <c r="H127">
+        <v>11</v>
+      </c>
+      <c r="I127">
+        <v>1</v>
+      </c>
+      <c r="K127">
+        <v>41.8169895</v>
+      </c>
+      <c r="L127">
+        <v>-87.6996915</v>
+      </c>
+    </row>
+    <row r="128" spans="1:12">
+      <c r="B128" t="s">
+        <v>23</v>
+      </c>
+      <c r="C128" t="s">
+        <v>119</v>
+      </c>
+      <c r="D128" t="s">
+        <v>226</v>
+      </c>
+      <c r="E128" t="s">
+        <v>241</v>
+      </c>
+      <c r="F128" t="s">
+        <v>322</v>
+      </c>
+      <c r="G128">
+        <v>1927</v>
+      </c>
+      <c r="H128">
+        <v>11</v>
+      </c>
+      <c r="I128">
+        <v>1</v>
+      </c>
+      <c r="K128">
+        <v>41.9033594</v>
+      </c>
+      <c r="L128">
+        <v>-87.67168820000001</v>
+      </c>
+    </row>
+    <row r="129" spans="2:13">
+      <c r="B129" t="s">
+        <v>49</v>
+      </c>
+      <c r="C129" t="s">
+        <v>122</v>
+      </c>
+      <c r="D129" t="s">
+        <v>186</v>
+      </c>
+      <c r="E129" t="s">
+        <v>312</v>
+      </c>
+      <c r="F129" t="s">
+        <v>322</v>
+      </c>
+      <c r="G129">
+        <v>1927</v>
+      </c>
+      <c r="H129">
+        <v>11</v>
+      </c>
+      <c r="I129">
+        <v>1</v>
+      </c>
+      <c r="K129">
+        <v>41.906892</v>
+      </c>
+      <c r="L129">
+        <v>-87.670137</v>
+      </c>
+    </row>
+    <row r="130" spans="2:13">
+      <c r="B130" t="s">
+        <v>108</v>
+      </c>
+      <c r="C130" t="s">
+        <v>136</v>
+      </c>
+      <c r="D130" t="s">
+        <v>186</v>
+      </c>
+      <c r="E130" t="s">
+        <v>313</v>
+      </c>
+      <c r="F130" t="s">
+        <v>322</v>
+      </c>
+      <c r="G130">
+        <v>1927</v>
+      </c>
+      <c r="H130">
+        <v>11</v>
+      </c>
+      <c r="I130">
+        <v>1</v>
+      </c>
+      <c r="K130">
+        <v>41.900223</v>
+      </c>
+      <c r="L130">
+        <v>-87.6720337</v>
+      </c>
+    </row>
+    <row r="131" spans="2:13">
+      <c r="B131" t="s">
+        <v>109</v>
+      </c>
+      <c r="C131" t="s">
+        <v>132</v>
+      </c>
+      <c r="D131" t="s">
+        <v>227</v>
+      </c>
+      <c r="E131" t="s">
+        <v>314</v>
+      </c>
+      <c r="F131" t="s">
+        <v>322</v>
+      </c>
+      <c r="G131">
+        <v>1927</v>
+      </c>
+      <c r="H131">
+        <v>11</v>
+      </c>
+      <c r="I131">
+        <v>1</v>
+      </c>
+      <c r="K131">
+        <v>42.1902504</v>
+      </c>
+      <c r="L131">
+        <v>-88.10135940000001</v>
+      </c>
+    </row>
+    <row r="132" spans="2:13">
+      <c r="B132" t="s">
+        <v>110</v>
+      </c>
+      <c r="C132" t="s">
+        <v>134</v>
+      </c>
+      <c r="D132" t="s">
+        <v>228</v>
+      </c>
+      <c r="E132" t="s">
+        <v>315</v>
+      </c>
+      <c r="F132" t="s">
+        <v>322</v>
+      </c>
+      <c r="G132">
+        <v>1927</v>
+      </c>
+      <c r="H132">
+        <v>11</v>
+      </c>
+      <c r="I132">
+        <v>1</v>
+      </c>
+      <c r="K132">
+        <v>41.8735823</v>
+      </c>
+      <c r="L132">
+        <v>-87.6245054</v>
+      </c>
+    </row>
+    <row r="133" spans="2:13">
+      <c r="B133" t="s">
+        <v>111</v>
+      </c>
+      <c r="C133" t="s">
+        <v>142</v>
+      </c>
+      <c r="D133" t="s">
+        <v>229</v>
+      </c>
+      <c r="E133" t="s">
+        <v>157</v>
+      </c>
+      <c r="F133" t="s">
+        <v>322</v>
+      </c>
+      <c r="G133">
+        <v>1927</v>
+      </c>
+      <c r="H133">
+        <v>11</v>
+      </c>
+      <c r="I133">
+        <v>1</v>
+      </c>
+      <c r="K133">
+        <v>41.8768707</v>
+      </c>
+      <c r="L133">
+        <v>-87.6261645</v>
+      </c>
+    </row>
+    <row r="134" spans="2:13">
+      <c r="B134" t="s">
+        <v>111</v>
+      </c>
+      <c r="C134" t="s">
+        <v>134</v>
+      </c>
+      <c r="D134" t="s">
+        <v>229</v>
+      </c>
+      <c r="E134" t="s">
+        <v>316</v>
+      </c>
+      <c r="F134" t="s">
+        <v>322</v>
+      </c>
+      <c r="G134">
+        <v>1927</v>
+      </c>
+      <c r="H134">
+        <v>11</v>
+      </c>
+      <c r="I134">
+        <v>1</v>
+      </c>
+      <c r="K134">
+        <v>41.8768707</v>
+      </c>
+      <c r="L134">
+        <v>-87.6261645</v>
+      </c>
+    </row>
+    <row r="135" spans="2:13">
+      <c r="B135" t="s">
+        <v>112</v>
+      </c>
+      <c r="C135" t="s">
+        <v>139</v>
+      </c>
+      <c r="D135" t="s">
+        <v>230</v>
+      </c>
+      <c r="E135" t="s">
+        <v>317</v>
+      </c>
+      <c r="F135" t="s">
+        <v>322</v>
+      </c>
+      <c r="G135">
+        <v>1927</v>
+      </c>
+      <c r="H135">
+        <v>11</v>
+      </c>
+      <c r="I135">
+        <v>1</v>
+      </c>
+      <c r="K135">
+        <v>41.8634429</v>
+      </c>
+      <c r="L135">
+        <v>-87.6601778</v>
+      </c>
+    </row>
+    <row r="136" spans="2:13">
+      <c r="B136" t="s">
+        <v>113</v>
+      </c>
+      <c r="C136" t="s">
+        <v>139</v>
+      </c>
+      <c r="D136" t="s">
+        <v>181</v>
+      </c>
+      <c r="E136" t="s">
+        <v>318</v>
+      </c>
+      <c r="F136" t="s">
+        <v>322</v>
+      </c>
+      <c r="G136">
+        <v>1927</v>
+      </c>
+      <c r="H136">
+        <v>11</v>
+      </c>
+      <c r="I136">
+        <v>1</v>
+      </c>
+      <c r="K136">
+        <v>41.7030387101996</v>
+      </c>
+      <c r="L136">
+        <v>-87.6046693625252</v>
+      </c>
+    </row>
+    <row r="137" spans="2:13">
+      <c r="B137" t="s">
+        <v>114</v>
+      </c>
+      <c r="C137" t="s">
+        <v>119</v>
+      </c>
+      <c r="D137" t="s">
+        <v>231</v>
+      </c>
+      <c r="E137" t="s">
+        <v>242</v>
+      </c>
+      <c r="F137" t="s">
+        <v>322</v>
+      </c>
+      <c r="G137">
+        <v>1927</v>
+      </c>
+      <c r="H137">
+        <v>12</v>
+      </c>
+      <c r="I137">
+        <v>1</v>
+      </c>
+      <c r="K137">
+        <v>41.9037547</v>
+      </c>
+      <c r="L137">
+        <v>-87.66752320000001</v>
+      </c>
+    </row>
+    <row r="138" spans="2:13">
+      <c r="B138" t="s">
+        <v>115</v>
+      </c>
+      <c r="C138" t="s">
+        <v>138</v>
+      </c>
+      <c r="D138" t="s">
+        <v>232</v>
+      </c>
+      <c r="E138" t="s">
+        <v>319</v>
+      </c>
+      <c r="F138" t="s">
+        <v>322</v>
+      </c>
+      <c r="G138">
+        <v>1927</v>
+      </c>
+      <c r="H138">
+        <v>12</v>
+      </c>
+      <c r="I138">
+        <v>1</v>
+      </c>
+      <c r="K138">
+        <v>41.8958009</v>
+      </c>
+      <c r="L138">
+        <v>-87.66692449999999</v>
+      </c>
+    </row>
+    <row r="139" spans="2:13">
+      <c r="B139" t="s">
+        <v>116</v>
+      </c>
+      <c r="C139" t="s">
+        <v>132</v>
+      </c>
+      <c r="D139" t="s">
+        <v>186</v>
+      </c>
+      <c r="E139" t="s">
+        <v>320</v>
+      </c>
+      <c r="F139" t="s">
+        <v>322</v>
+      </c>
+      <c r="G139">
+        <v>1927</v>
+      </c>
+      <c r="H139">
+        <v>12</v>
+      </c>
+      <c r="I139">
+        <v>1</v>
+      </c>
+      <c r="K139">
+        <v>40.1816726</v>
+      </c>
+      <c r="L139">
+        <v>-91.377397</v>
+      </c>
+      <c r="M139" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="140" spans="2:13">
+      <c r="B140" t="s">
+        <v>117</v>
+      </c>
+      <c r="C140" t="s">
+        <v>134</v>
+      </c>
+      <c r="D140" t="s">
+        <v>233</v>
+      </c>
+      <c r="E140" t="s">
+        <v>321</v>
+      </c>
+      <c r="F140" t="s">
+        <v>322</v>
+      </c>
+      <c r="G140">
+        <v>1927</v>
+      </c>
+      <c r="H140">
+        <v>12</v>
+      </c>
+      <c r="I140">
+        <v>1</v>
+      </c>
+      <c r="K140">
+        <v>41.8779893</v>
+      </c>
+      <c r="L140">
+        <v>-87.6246979</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="J2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="J3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="J4" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="J5" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="J6" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="J7" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="J8" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="J9" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
-    <hyperlink ref="J10" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
-    <hyperlink ref="J11" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
-    <hyperlink ref="J12" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
-    <hyperlink ref="J13" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
-    <hyperlink ref="J14" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
-    <hyperlink ref="J15" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
-    <hyperlink ref="J16" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
-    <hyperlink ref="J17" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
-    <hyperlink ref="J18" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
-    <hyperlink ref="J19" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
-    <hyperlink ref="J20" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
-    <hyperlink ref="J21" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
-    <hyperlink ref="J22" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
-    <hyperlink ref="J23" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
-    <hyperlink ref="J24" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
-    <hyperlink ref="J25" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
-    <hyperlink ref="J26" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
-    <hyperlink ref="J27" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
-    <hyperlink ref="J28" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
-    <hyperlink ref="J29" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
-    <hyperlink ref="J30" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
-    <hyperlink ref="J31" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
-    <hyperlink ref="J32" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
-    <hyperlink ref="J33" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
-    <hyperlink ref="J34" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
-    <hyperlink ref="J35" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
-    <hyperlink ref="J36" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
-    <hyperlink ref="J37" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
-    <hyperlink ref="J38" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
-    <hyperlink ref="J39" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
-    <hyperlink ref="J40" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
-    <hyperlink ref="J41" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
-    <hyperlink ref="J42" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
-    <hyperlink ref="J43" r:id="rId42" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
-    <hyperlink ref="J44" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
-    <hyperlink ref="J45" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
-    <hyperlink ref="J46" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
-    <hyperlink ref="J47" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
-    <hyperlink ref="J48" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
-    <hyperlink ref="J49" r:id="rId48" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
-    <hyperlink ref="J50" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
-    <hyperlink ref="J51" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
-    <hyperlink ref="J52" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
-    <hyperlink ref="J53" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
-    <hyperlink ref="J54" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
-    <hyperlink ref="J55" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
-    <hyperlink ref="J56" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
-    <hyperlink ref="J57" r:id="rId56" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
-    <hyperlink ref="J58" r:id="rId57" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
-    <hyperlink ref="J59" r:id="rId58" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
-    <hyperlink ref="J60" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
-    <hyperlink ref="J61" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
-    <hyperlink ref="J62" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
-    <hyperlink ref="J63" r:id="rId62" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
-    <hyperlink ref="J64" r:id="rId63" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
-    <hyperlink ref="J65" r:id="rId64" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
-    <hyperlink ref="J66" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
-    <hyperlink ref="J67" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
-    <hyperlink ref="J68" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
-    <hyperlink ref="J69" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
-    <hyperlink ref="J70" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
-    <hyperlink ref="J71" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
+    <hyperlink ref="J2" r:id="rId1"/>
+    <hyperlink ref="J3" r:id="rId2"/>
+    <hyperlink ref="J4" r:id="rId3"/>
+    <hyperlink ref="J5" r:id="rId4"/>
+    <hyperlink ref="J6" r:id="rId5"/>
+    <hyperlink ref="J7" r:id="rId6"/>
+    <hyperlink ref="J8" r:id="rId7"/>
+    <hyperlink ref="J9" r:id="rId8"/>
+    <hyperlink ref="J10" r:id="rId9"/>
+    <hyperlink ref="J11" r:id="rId10"/>
+    <hyperlink ref="J12" r:id="rId11"/>
+    <hyperlink ref="J13" r:id="rId12"/>
+    <hyperlink ref="J14" r:id="rId13"/>
+    <hyperlink ref="J15" r:id="rId14"/>
+    <hyperlink ref="J16" r:id="rId15"/>
+    <hyperlink ref="J17" r:id="rId16"/>
+    <hyperlink ref="J18" r:id="rId17"/>
+    <hyperlink ref="J19" r:id="rId18"/>
+    <hyperlink ref="J20" r:id="rId19"/>
+    <hyperlink ref="J21" r:id="rId20"/>
+    <hyperlink ref="J22" r:id="rId21"/>
+    <hyperlink ref="J23" r:id="rId22"/>
+    <hyperlink ref="J24" r:id="rId23"/>
+    <hyperlink ref="J25" r:id="rId24"/>
+    <hyperlink ref="J26" r:id="rId25"/>
+    <hyperlink ref="J27" r:id="rId26"/>
+    <hyperlink ref="J28" r:id="rId27"/>
+    <hyperlink ref="J29" r:id="rId28"/>
+    <hyperlink ref="J30" r:id="rId29"/>
+    <hyperlink ref="J31" r:id="rId30"/>
+    <hyperlink ref="J32" r:id="rId31"/>
+    <hyperlink ref="J33" r:id="rId32"/>
+    <hyperlink ref="J34" r:id="rId33"/>
+    <hyperlink ref="J35" r:id="rId34"/>
+    <hyperlink ref="J36" r:id="rId35"/>
+    <hyperlink ref="J37" r:id="rId36"/>
+    <hyperlink ref="J38" r:id="rId37"/>
+    <hyperlink ref="J39" r:id="rId38"/>
+    <hyperlink ref="J40" r:id="rId39"/>
+    <hyperlink ref="J41" r:id="rId40"/>
+    <hyperlink ref="J42" r:id="rId41"/>
+    <hyperlink ref="J43" r:id="rId42"/>
+    <hyperlink ref="J44" r:id="rId43"/>
+    <hyperlink ref="J45" r:id="rId44"/>
+    <hyperlink ref="J46" r:id="rId45"/>
+    <hyperlink ref="J47" r:id="rId46"/>
+    <hyperlink ref="J48" r:id="rId47"/>
+    <hyperlink ref="J49" r:id="rId48"/>
+    <hyperlink ref="J50" r:id="rId49"/>
+    <hyperlink ref="J51" r:id="rId50"/>
+    <hyperlink ref="J52" r:id="rId51"/>
+    <hyperlink ref="J53" r:id="rId52"/>
+    <hyperlink ref="J54" r:id="rId53"/>
+    <hyperlink ref="J55" r:id="rId54"/>
+    <hyperlink ref="J56" r:id="rId55"/>
+    <hyperlink ref="J57" r:id="rId56"/>
+    <hyperlink ref="J58" r:id="rId57"/>
+    <hyperlink ref="J59" r:id="rId58"/>
+    <hyperlink ref="J60" r:id="rId59"/>
+    <hyperlink ref="J61" r:id="rId60"/>
+    <hyperlink ref="J62" r:id="rId61"/>
+    <hyperlink ref="J63" r:id="rId62"/>
+    <hyperlink ref="J64" r:id="rId63"/>
+    <hyperlink ref="J65" r:id="rId64"/>
+    <hyperlink ref="J66" r:id="rId65"/>
+    <hyperlink ref="J67" r:id="rId66"/>
+    <hyperlink ref="J68" r:id="rId67"/>
+    <hyperlink ref="J69" r:id="rId68"/>
+    <hyperlink ref="J70" r:id="rId69"/>
+    <hyperlink ref="J71" r:id="rId70"/>
+    <hyperlink ref="J72" r:id="rId71"/>
+    <hyperlink ref="J73" r:id="rId72"/>
+    <hyperlink ref="J74" r:id="rId73"/>
+    <hyperlink ref="J75" r:id="rId74"/>
+    <hyperlink ref="J76" r:id="rId75"/>
+    <hyperlink ref="J77" r:id="rId76"/>
+    <hyperlink ref="J78" r:id="rId77"/>
+    <hyperlink ref="J79" r:id="rId78"/>
+    <hyperlink ref="J80" r:id="rId79"/>
+    <hyperlink ref="J81" r:id="rId80"/>
+    <hyperlink ref="J82" r:id="rId81"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
